--- a/scripts/overload-simulation.xlsx
+++ b/scripts/overload-simulation.xlsx
@@ -526,7 +526,7 @@
         <v>32.5</v>
       </c>
       <c r="I2">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="J2">
         <v>3</v>
@@ -535,7 +535,7 @@
         <v>3</v>
       </c>
       <c r="L2">
-        <v>780</v>
+        <v>975</v>
       </c>
       <c r="M2" t="str">
         <v>First session</v>
@@ -582,7 +582,7 @@
         <v>32.5</v>
       </c>
       <c r="I3">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="J3">
         <v>2</v>
@@ -591,7 +591,7 @@
         <v>2</v>
       </c>
       <c r="L3">
-        <v>1170</v>
+        <v>1430</v>
       </c>
       <c r="M3" t="str">
         <v>+1 REP</v>
@@ -638,7 +638,7 @@
         <v>32.5</v>
       </c>
       <c r="I4">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="J4">
         <v>1</v>
@@ -647,7 +647,7 @@
         <v>1</v>
       </c>
       <c r="L4">
-        <v>1625</v>
+        <v>1950</v>
       </c>
       <c r="M4" t="str">
         <v>+1 REP</v>
@@ -694,7 +694,7 @@
         <v>32.5</v>
       </c>
       <c r="I5">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="J5">
         <v>0</v>
@@ -703,13 +703,13 @@
         <v>0</v>
       </c>
       <c r="L5">
-        <v>2145</v>
+        <v>2340</v>
       </c>
       <c r="M5" t="str">
-        <v>+1 REP</v>
+        <v>→ HOLD</v>
       </c>
       <c r="N5" t="str">
-        <v>RIR 1 &gt; target 0 → +1 rep</v>
+        <v>12@RIR1 on track</v>
       </c>
       <c r="O5" t="str">
         <v/>
@@ -747,10 +747,10 @@
         <v>5</v>
       </c>
       <c r="H6">
-        <v>30</v>
+        <v>32.5</v>
       </c>
       <c r="I6">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="J6">
         <v>0</v>
@@ -759,13 +759,13 @@
         <v>0</v>
       </c>
       <c r="L6">
-        <v>1650</v>
+        <v>1300</v>
       </c>
       <c r="M6" t="str">
-        <v>→ HOLD</v>
+        <v>↑ WEIGHT</v>
       </c>
       <c r="N6" t="str">
-        <v>11@RIR0 on track</v>
+        <v>Hit 12@RIR0 = top of range → +2.5 kg</v>
       </c>
       <c r="O6" t="str">
         <v/>
@@ -806,7 +806,7 @@
         <v>60</v>
       </c>
       <c r="I7">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="J7">
         <v>3</v>
@@ -815,7 +815,7 @@
         <v>3</v>
       </c>
       <c r="L7">
-        <v>1800</v>
+        <v>2340</v>
       </c>
       <c r="M7" t="str">
         <v>First session</v>
@@ -862,7 +862,7 @@
         <v>60</v>
       </c>
       <c r="I8">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="J8">
         <v>2</v>
@@ -871,7 +871,7 @@
         <v>2</v>
       </c>
       <c r="L8">
-        <v>2640</v>
+        <v>3360</v>
       </c>
       <c r="M8" t="str">
         <v>+1 REP</v>
@@ -918,7 +918,7 @@
         <v>60</v>
       </c>
       <c r="I9">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="J9">
         <v>1</v>
@@ -927,7 +927,7 @@
         <v>1</v>
       </c>
       <c r="L9">
-        <v>3600</v>
+        <v>4500</v>
       </c>
       <c r="M9" t="str">
         <v>+1 REP</v>
@@ -974,7 +974,7 @@
         <v>60</v>
       </c>
       <c r="I10">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="J10">
         <v>0</v>
@@ -983,13 +983,13 @@
         <v>0</v>
       </c>
       <c r="L10">
-        <v>4680</v>
+        <v>5400</v>
       </c>
       <c r="M10" t="str">
-        <v>+1 REP</v>
+        <v>→ HOLD</v>
       </c>
       <c r="N10" t="str">
-        <v>RIR 1 &gt; target 0 → +1 rep</v>
+        <v>15@RIR1 on track</v>
       </c>
       <c r="O10" t="str">
         <v/>
@@ -1027,10 +1027,10 @@
         <v>5</v>
       </c>
       <c r="H11">
-        <v>57.5</v>
+        <v>60</v>
       </c>
       <c r="I11">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="J11">
         <v>0</v>
@@ -1039,13 +1039,13 @@
         <v>0</v>
       </c>
       <c r="L11">
-        <v>3737.5</v>
+        <v>3000</v>
       </c>
       <c r="M11" t="str">
-        <v>→ HOLD</v>
+        <v>↑ WEIGHT</v>
       </c>
       <c r="N11" t="str">
-        <v>13@RIR0 on track</v>
+        <v>Hit 15@RIR0 = top of range → +2.5 kg</v>
       </c>
       <c r="O11" t="str">
         <v/>
@@ -1086,7 +1086,7 @@
         <v>10</v>
       </c>
       <c r="I12">
-        <v>12</v>
+        <v>18</v>
       </c>
       <c r="J12">
         <v>3</v>
@@ -1095,7 +1095,7 @@
         <v>3</v>
       </c>
       <c r="L12">
-        <v>360</v>
+        <v>540</v>
       </c>
       <c r="M12" t="str">
         <v>First session</v>
@@ -1142,7 +1142,7 @@
         <v>10</v>
       </c>
       <c r="I13">
-        <v>13</v>
+        <v>19</v>
       </c>
       <c r="J13">
         <v>2</v>
@@ -1151,7 +1151,7 @@
         <v>2</v>
       </c>
       <c r="L13">
-        <v>520</v>
+        <v>760</v>
       </c>
       <c r="M13" t="str">
         <v>+1 REP</v>
@@ -1198,7 +1198,7 @@
         <v>10</v>
       </c>
       <c r="I14">
-        <v>14</v>
+        <v>20</v>
       </c>
       <c r="J14">
         <v>1</v>
@@ -1207,7 +1207,7 @@
         <v>1</v>
       </c>
       <c r="L14">
-        <v>700</v>
+        <v>1000</v>
       </c>
       <c r="M14" t="str">
         <v>+1 REP</v>
@@ -1254,7 +1254,7 @@
         <v>10</v>
       </c>
       <c r="I15">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="J15">
         <v>0</v>
@@ -1263,13 +1263,13 @@
         <v>0</v>
       </c>
       <c r="L15">
-        <v>900</v>
+        <v>1200</v>
       </c>
       <c r="M15" t="str">
-        <v>+1 REP</v>
+        <v>→ HOLD</v>
       </c>
       <c r="N15" t="str">
-        <v>RIR 1 &gt; target 0 → +1 rep</v>
+        <v>20@RIR1 on track</v>
       </c>
       <c r="O15" t="str">
         <v/>
@@ -1310,7 +1310,7 @@
         <v>10</v>
       </c>
       <c r="I16">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="J16">
         <v>0</v>
@@ -1319,13 +1319,13 @@
         <v>0</v>
       </c>
       <c r="L16">
-        <v>900</v>
+        <v>720</v>
       </c>
       <c r="M16" t="str">
-        <v>→ HOLD</v>
+        <v>↑ WEIGHT</v>
       </c>
       <c r="N16" t="str">
-        <v>15@RIR0 on track</v>
+        <v>Hit 20@RIR0 = top of range → +2.5 kg</v>
       </c>
       <c r="O16" t="str">
         <v/>
@@ -1366,7 +1366,7 @@
         <v>25</v>
       </c>
       <c r="I17">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="J17">
         <v>3</v>
@@ -1375,7 +1375,7 @@
         <v>3</v>
       </c>
       <c r="L17">
-        <v>750</v>
+        <v>975</v>
       </c>
       <c r="M17" t="str">
         <v>First session</v>
@@ -1422,7 +1422,7 @@
         <v>25</v>
       </c>
       <c r="I18">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="J18">
         <v>2</v>
@@ -1431,7 +1431,7 @@
         <v>2</v>
       </c>
       <c r="L18">
-        <v>1100</v>
+        <v>1400</v>
       </c>
       <c r="M18" t="str">
         <v>+1 REP</v>
@@ -1478,7 +1478,7 @@
         <v>25</v>
       </c>
       <c r="I19">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="J19">
         <v>1</v>
@@ -1487,7 +1487,7 @@
         <v>1</v>
       </c>
       <c r="L19">
-        <v>1500</v>
+        <v>1875</v>
       </c>
       <c r="M19" t="str">
         <v>+1 REP</v>
@@ -1534,7 +1534,7 @@
         <v>25</v>
       </c>
       <c r="I20">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="J20">
         <v>0</v>
@@ -1543,13 +1543,13 @@
         <v>0</v>
       </c>
       <c r="L20">
-        <v>1950</v>
+        <v>2250</v>
       </c>
       <c r="M20" t="str">
-        <v>+1 REP</v>
+        <v>→ HOLD</v>
       </c>
       <c r="N20" t="str">
-        <v>RIR 1 &gt; target 0 → +1 rep</v>
+        <v>15@RIR1 on track</v>
       </c>
       <c r="O20" t="str">
         <v/>
@@ -1587,10 +1587,10 @@
         <v>6</v>
       </c>
       <c r="H21">
-        <v>25</v>
+        <v>27.5</v>
       </c>
       <c r="I21">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="J21">
         <v>0</v>
@@ -1599,13 +1599,13 @@
         <v>0</v>
       </c>
       <c r="L21">
-        <v>1950</v>
+        <v>1650</v>
       </c>
       <c r="M21" t="str">
-        <v>→ HOLD</v>
+        <v>↑ WEIGHT</v>
       </c>
       <c r="N21" t="str">
-        <v>13@RIR0 on track</v>
+        <v>Hit 15@RIR0 = top of range → +2.5 kg</v>
       </c>
       <c r="O21" t="str">
         <v/>
@@ -1646,7 +1646,7 @@
         <v>55</v>
       </c>
       <c r="I22">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="J22">
         <v>3</v>
@@ -1655,7 +1655,7 @@
         <v>3</v>
       </c>
       <c r="L22">
-        <v>1320</v>
+        <v>1650</v>
       </c>
       <c r="M22" t="str">
         <v>First session</v>
@@ -1702,7 +1702,7 @@
         <v>55</v>
       </c>
       <c r="I23">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="J23">
         <v>2</v>
@@ -1711,7 +1711,7 @@
         <v>2</v>
       </c>
       <c r="L23">
-        <v>1980</v>
+        <v>2420</v>
       </c>
       <c r="M23" t="str">
         <v>+1 REP</v>
@@ -1758,7 +1758,7 @@
         <v>55</v>
       </c>
       <c r="I24">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="J24">
         <v>1</v>
@@ -1767,7 +1767,7 @@
         <v>1</v>
       </c>
       <c r="L24">
-        <v>2750</v>
+        <v>3300</v>
       </c>
       <c r="M24" t="str">
         <v>+1 REP</v>
@@ -1814,7 +1814,7 @@
         <v>55</v>
       </c>
       <c r="I25">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="J25">
         <v>0</v>
@@ -1823,13 +1823,13 @@
         <v>0</v>
       </c>
       <c r="L25">
-        <v>3630</v>
+        <v>3960</v>
       </c>
       <c r="M25" t="str">
-        <v>+1 REP</v>
+        <v>→ HOLD</v>
       </c>
       <c r="N25" t="str">
-        <v>RIR 1 &gt; target 0 → +1 rep</v>
+        <v>12@RIR1 on track</v>
       </c>
       <c r="O25" t="str">
         <v/>
@@ -1867,10 +1867,10 @@
         <v>4</v>
       </c>
       <c r="H26">
-        <v>50</v>
+        <v>52.5</v>
       </c>
       <c r="I26">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="J26">
         <v>0</v>
@@ -1879,13 +1879,13 @@
         <v>0</v>
       </c>
       <c r="L26">
-        <v>2200</v>
+        <v>1680</v>
       </c>
       <c r="M26" t="str">
-        <v>→ HOLD</v>
+        <v>↑ WEIGHT</v>
       </c>
       <c r="N26" t="str">
-        <v>11@RIR0 on track</v>
+        <v>Hit 12@RIR0 = top of range → +2.5 kg</v>
       </c>
       <c r="O26" t="str">
         <v/>
@@ -1926,7 +1926,7 @@
         <v>60</v>
       </c>
       <c r="I27">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="J27">
         <v>3</v>
@@ -1935,7 +1935,7 @@
         <v>3</v>
       </c>
       <c r="L27">
-        <v>1440</v>
+        <v>1800</v>
       </c>
       <c r="M27" t="str">
         <v>First session</v>
@@ -1982,7 +1982,7 @@
         <v>60</v>
       </c>
       <c r="I28">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="J28">
         <v>2</v>
@@ -1991,7 +1991,7 @@
         <v>2</v>
       </c>
       <c r="L28">
-        <v>2160</v>
+        <v>2640</v>
       </c>
       <c r="M28" t="str">
         <v>+1 REP</v>
@@ -2038,7 +2038,7 @@
         <v>60</v>
       </c>
       <c r="I29">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="J29">
         <v>1</v>
@@ -2047,7 +2047,7 @@
         <v>1</v>
       </c>
       <c r="L29">
-        <v>3000</v>
+        <v>3600</v>
       </c>
       <c r="M29" t="str">
         <v>+1 REP</v>
@@ -2094,7 +2094,7 @@
         <v>60</v>
       </c>
       <c r="I30">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="J30">
         <v>0</v>
@@ -2103,13 +2103,13 @@
         <v>0</v>
       </c>
       <c r="L30">
-        <v>3960</v>
+        <v>4320</v>
       </c>
       <c r="M30" t="str">
-        <v>+1 REP</v>
+        <v>→ HOLD</v>
       </c>
       <c r="N30" t="str">
-        <v>RIR 1 &gt; target 0 → +1 rep</v>
+        <v>12@RIR1 on track</v>
       </c>
       <c r="O30" t="str">
         <v/>
@@ -2147,10 +2147,10 @@
         <v>4</v>
       </c>
       <c r="H31">
-        <v>55</v>
+        <v>57.5</v>
       </c>
       <c r="I31">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="J31">
         <v>0</v>
@@ -2159,13 +2159,13 @@
         <v>0</v>
       </c>
       <c r="L31">
-        <v>2420</v>
+        <v>1840</v>
       </c>
       <c r="M31" t="str">
-        <v>→ HOLD</v>
+        <v>↑ WEIGHT</v>
       </c>
       <c r="N31" t="str">
-        <v>11@RIR0 on track</v>
+        <v>Hit 12@RIR0 = top of range → +2.5 kg</v>
       </c>
       <c r="O31" t="str">
         <v/>
@@ -2206,7 +2206,7 @@
         <v>12.5</v>
       </c>
       <c r="I32">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="J32">
         <v>3</v>
@@ -2215,7 +2215,7 @@
         <v>3</v>
       </c>
       <c r="L32">
-        <v>375</v>
+        <v>487.5</v>
       </c>
       <c r="M32" t="str">
         <v>First session</v>
@@ -2262,7 +2262,7 @@
         <v>12.5</v>
       </c>
       <c r="I33">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="J33">
         <v>2</v>
@@ -2271,7 +2271,7 @@
         <v>2</v>
       </c>
       <c r="L33">
-        <v>550</v>
+        <v>700</v>
       </c>
       <c r="M33" t="str">
         <v>+1 REP</v>
@@ -2318,7 +2318,7 @@
         <v>12.5</v>
       </c>
       <c r="I34">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="J34">
         <v>1</v>
@@ -2327,7 +2327,7 @@
         <v>1</v>
       </c>
       <c r="L34">
-        <v>750</v>
+        <v>937.5</v>
       </c>
       <c r="M34" t="str">
         <v>+1 REP</v>
@@ -2374,7 +2374,7 @@
         <v>12.5</v>
       </c>
       <c r="I35">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="J35">
         <v>0</v>
@@ -2383,13 +2383,13 @@
         <v>0</v>
       </c>
       <c r="L35">
-        <v>975</v>
+        <v>1125</v>
       </c>
       <c r="M35" t="str">
-        <v>+1 REP</v>
+        <v>→ HOLD</v>
       </c>
       <c r="N35" t="str">
-        <v>RIR 1 &gt; target 0 → +1 rep</v>
+        <v>15@RIR1 on track</v>
       </c>
       <c r="O35" t="str">
         <v/>
@@ -2430,7 +2430,7 @@
         <v>12.5</v>
       </c>
       <c r="I36">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="J36">
         <v>0</v>
@@ -2439,13 +2439,13 @@
         <v>0</v>
       </c>
       <c r="L36">
-        <v>650</v>
+        <v>500</v>
       </c>
       <c r="M36" t="str">
-        <v>→ HOLD</v>
+        <v>↑ WEIGHT</v>
       </c>
       <c r="N36" t="str">
-        <v>13@RIR0 on track</v>
+        <v>Hit 15@RIR0 = top of range → +2.5 kg</v>
       </c>
       <c r="O36" t="str">
         <v/>
@@ -2486,7 +2486,7 @@
         <v>15</v>
       </c>
       <c r="I37">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="J37">
         <v>3</v>
@@ -2495,7 +2495,7 @@
         <v>3</v>
       </c>
       <c r="L37">
-        <v>300</v>
+        <v>390</v>
       </c>
       <c r="M37" t="str">
         <v>First session</v>
@@ -2542,7 +2542,7 @@
         <v>15</v>
       </c>
       <c r="I38">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="J38">
         <v>2</v>
@@ -2551,7 +2551,7 @@
         <v>2</v>
       </c>
       <c r="L38">
-        <v>495</v>
+        <v>630</v>
       </c>
       <c r="M38" t="str">
         <v>+1 REP</v>
@@ -2598,7 +2598,7 @@
         <v>15</v>
       </c>
       <c r="I39">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="J39">
         <v>1</v>
@@ -2607,7 +2607,7 @@
         <v>1</v>
       </c>
       <c r="L39">
-        <v>720</v>
+        <v>900</v>
       </c>
       <c r="M39" t="str">
         <v>+1 REP</v>
@@ -2654,7 +2654,7 @@
         <v>15</v>
       </c>
       <c r="I40">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="J40">
         <v>0</v>
@@ -2663,13 +2663,13 @@
         <v>0</v>
       </c>
       <c r="L40">
-        <v>975</v>
+        <v>1125</v>
       </c>
       <c r="M40" t="str">
-        <v>+1 REP</v>
+        <v>→ HOLD</v>
       </c>
       <c r="N40" t="str">
-        <v>RIR 1 &gt; target 0 → +1 rep</v>
+        <v>15@RIR1 on track</v>
       </c>
       <c r="O40" t="str">
         <v/>
@@ -2707,10 +2707,10 @@
         <v>3</v>
       </c>
       <c r="H41">
-        <v>12.5</v>
+        <v>15</v>
       </c>
       <c r="I41">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="J41">
         <v>0</v>
@@ -2719,13 +2719,13 @@
         <v>0</v>
       </c>
       <c r="L41">
-        <v>487.5</v>
+        <v>450</v>
       </c>
       <c r="M41" t="str">
-        <v>→ HOLD</v>
+        <v>↑ WEIGHT</v>
       </c>
       <c r="N41" t="str">
-        <v>13@RIR0 on track</v>
+        <v>Hit 15@RIR0 = top of range → +2.5 kg</v>
       </c>
       <c r="O41" t="str">
         <v/>
@@ -2766,7 +2766,7 @@
         <v>120</v>
       </c>
       <c r="I42">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="J42">
         <v>3</v>
@@ -2775,7 +2775,7 @@
         <v>3</v>
       </c>
       <c r="L42">
-        <v>2880</v>
+        <v>3600</v>
       </c>
       <c r="M42" t="str">
         <v>First session</v>
@@ -2822,7 +2822,7 @@
         <v>120</v>
       </c>
       <c r="I43">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="J43">
         <v>2</v>
@@ -2831,7 +2831,7 @@
         <v>2</v>
       </c>
       <c r="L43">
-        <v>4320</v>
+        <v>5280</v>
       </c>
       <c r="M43" t="str">
         <v>+1 REP</v>
@@ -2878,7 +2878,7 @@
         <v>120</v>
       </c>
       <c r="I44">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="J44">
         <v>1</v>
@@ -2887,7 +2887,7 @@
         <v>1</v>
       </c>
       <c r="L44">
-        <v>6000</v>
+        <v>7200</v>
       </c>
       <c r="M44" t="str">
         <v>+1 REP</v>
@@ -2934,7 +2934,7 @@
         <v>107.5</v>
       </c>
       <c r="I45">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="J45">
         <v>0</v>
@@ -2943,13 +2943,13 @@
         <v>0</v>
       </c>
       <c r="L45">
-        <v>4730</v>
+        <v>5160</v>
       </c>
       <c r="M45" t="str">
-        <v>+1 REP</v>
+        <v>→ HOLD</v>
       </c>
       <c r="N45" t="str">
-        <v>RIR 1 &gt; target 0 → +1 rep</v>
+        <v>12@RIR1 on track</v>
       </c>
       <c r="O45" t="str">
         <v/>
@@ -2987,10 +2987,10 @@
         <v>4</v>
       </c>
       <c r="H46">
-        <v>97.5</v>
+        <v>100</v>
       </c>
       <c r="I46">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="J46">
         <v>0</v>
@@ -2999,13 +2999,13 @@
         <v>0</v>
       </c>
       <c r="L46">
-        <v>4290</v>
+        <v>3200</v>
       </c>
       <c r="M46" t="str">
-        <v>→ HOLD</v>
+        <v>↑ WEIGHT</v>
       </c>
       <c r="N46" t="str">
-        <v>11@RIR0 on track</v>
+        <v>Hit 12@RIR0 = top of range → +2.5 kg</v>
       </c>
       <c r="O46" t="str">
         <v/>
@@ -3046,7 +3046,7 @@
         <v>50</v>
       </c>
       <c r="I47">
-        <v>12</v>
+        <v>18</v>
       </c>
       <c r="J47">
         <v>3</v>
@@ -3055,7 +3055,7 @@
         <v>3</v>
       </c>
       <c r="L47">
-        <v>1800</v>
+        <v>2700</v>
       </c>
       <c r="M47" t="str">
         <v>First session</v>
@@ -3102,7 +3102,7 @@
         <v>50</v>
       </c>
       <c r="I48">
-        <v>13</v>
+        <v>19</v>
       </c>
       <c r="J48">
         <v>2</v>
@@ -3111,7 +3111,7 @@
         <v>2</v>
       </c>
       <c r="L48">
-        <v>2600</v>
+        <v>3800</v>
       </c>
       <c r="M48" t="str">
         <v>+1 REP</v>
@@ -3158,7 +3158,7 @@
         <v>50</v>
       </c>
       <c r="I49">
-        <v>14</v>
+        <v>20</v>
       </c>
       <c r="J49">
         <v>1</v>
@@ -3167,7 +3167,7 @@
         <v>1</v>
       </c>
       <c r="L49">
-        <v>3500</v>
+        <v>5000</v>
       </c>
       <c r="M49" t="str">
         <v>+1 REP</v>
@@ -3214,7 +3214,7 @@
         <v>45</v>
       </c>
       <c r="I50">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="J50">
         <v>0</v>
@@ -3223,13 +3223,13 @@
         <v>0</v>
       </c>
       <c r="L50">
-        <v>2700</v>
+        <v>3600</v>
       </c>
       <c r="M50" t="str">
-        <v>+1 REP</v>
+        <v>→ HOLD</v>
       </c>
       <c r="N50" t="str">
-        <v>RIR 1 &gt; target 0 → +1 rep</v>
+        <v>20@RIR1 on track</v>
       </c>
       <c r="O50" t="str">
         <v/>
@@ -3267,10 +3267,10 @@
         <v>4</v>
       </c>
       <c r="H51">
-        <v>40</v>
+        <v>42.5</v>
       </c>
       <c r="I51">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="J51">
         <v>0</v>
@@ -3279,13 +3279,13 @@
         <v>0</v>
       </c>
       <c r="L51">
-        <v>2400</v>
+        <v>2040</v>
       </c>
       <c r="M51" t="str">
-        <v>→ HOLD</v>
+        <v>↑ WEIGHT</v>
       </c>
       <c r="N51" t="str">
-        <v>15@RIR0 on track</v>
+        <v>Hit 20@RIR0 = top of range → +2.5 kg</v>
       </c>
       <c r="O51" t="str">
         <v/>
@@ -3326,7 +3326,7 @@
         <v>60</v>
       </c>
       <c r="I52">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="J52">
         <v>3</v>
@@ -3335,7 +3335,7 @@
         <v>3</v>
       </c>
       <c r="L52">
-        <v>1440</v>
+        <v>1800</v>
       </c>
       <c r="M52" t="str">
         <v>First session</v>
@@ -3382,7 +3382,7 @@
         <v>60</v>
       </c>
       <c r="I53">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="J53">
         <v>2</v>
@@ -3391,7 +3391,7 @@
         <v>2</v>
       </c>
       <c r="L53">
-        <v>2160</v>
+        <v>2640</v>
       </c>
       <c r="M53" t="str">
         <v>+1 REP</v>
@@ -3438,7 +3438,7 @@
         <v>60</v>
       </c>
       <c r="I54">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="J54">
         <v>1</v>
@@ -3447,7 +3447,7 @@
         <v>1</v>
       </c>
       <c r="L54">
-        <v>3000</v>
+        <v>3600</v>
       </c>
       <c r="M54" t="str">
         <v>+1 REP</v>
@@ -3494,7 +3494,7 @@
         <v>60</v>
       </c>
       <c r="I55">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="J55">
         <v>0</v>
@@ -3503,13 +3503,13 @@
         <v>0</v>
       </c>
       <c r="L55">
-        <v>3960</v>
+        <v>4320</v>
       </c>
       <c r="M55" t="str">
-        <v>+1 REP</v>
+        <v>→ HOLD</v>
       </c>
       <c r="N55" t="str">
-        <v>RIR 1 &gt; target 0 → +1 rep</v>
+        <v>12@RIR1 on track</v>
       </c>
       <c r="O55" t="str">
         <v/>
@@ -3547,10 +3547,10 @@
         <v>4</v>
       </c>
       <c r="H56">
-        <v>55</v>
+        <v>57.5</v>
       </c>
       <c r="I56">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="J56">
         <v>0</v>
@@ -3559,13 +3559,13 @@
         <v>0</v>
       </c>
       <c r="L56">
-        <v>2420</v>
+        <v>1840</v>
       </c>
       <c r="M56" t="str">
-        <v>→ HOLD</v>
+        <v>↑ WEIGHT</v>
       </c>
       <c r="N56" t="str">
-        <v>11@RIR0 on track</v>
+        <v>Hit 12@RIR0 = top of range → +2.5 kg</v>
       </c>
       <c r="O56" t="str">
         <v/>
@@ -3606,7 +3606,7 @@
         <v>40</v>
       </c>
       <c r="I57">
-        <v>10</v>
+        <v>18</v>
       </c>
       <c r="J57">
         <v>3</v>
@@ -3615,7 +3615,7 @@
         <v>3</v>
       </c>
       <c r="L57">
-        <v>1600</v>
+        <v>2880</v>
       </c>
       <c r="M57" t="str">
         <v>First session</v>
@@ -3662,7 +3662,7 @@
         <v>40</v>
       </c>
       <c r="I58">
-        <v>11</v>
+        <v>19</v>
       </c>
       <c r="J58">
         <v>2</v>
@@ -3671,7 +3671,7 @@
         <v>2</v>
       </c>
       <c r="L58">
-        <v>2200</v>
+        <v>3800</v>
       </c>
       <c r="M58" t="str">
         <v>+1 REP</v>
@@ -3718,7 +3718,7 @@
         <v>40</v>
       </c>
       <c r="I59">
-        <v>12</v>
+        <v>20</v>
       </c>
       <c r="J59">
         <v>1</v>
@@ -3727,7 +3727,7 @@
         <v>1</v>
       </c>
       <c r="L59">
-        <v>2880</v>
+        <v>4800</v>
       </c>
       <c r="M59" t="str">
         <v>+1 REP</v>
@@ -3774,7 +3774,7 @@
         <v>40</v>
       </c>
       <c r="I60">
-        <v>13</v>
+        <v>20</v>
       </c>
       <c r="J60">
         <v>0</v>
@@ -3783,13 +3783,13 @@
         <v>0</v>
       </c>
       <c r="L60">
-        <v>3640</v>
+        <v>5600</v>
       </c>
       <c r="M60" t="str">
-        <v>+1 REP</v>
+        <v>→ HOLD</v>
       </c>
       <c r="N60" t="str">
-        <v>RIR 1 &gt; target 0 → +1 rep</v>
+        <v>20@RIR1 on track</v>
       </c>
       <c r="O60" t="str">
         <v/>
@@ -3827,10 +3827,10 @@
         <v>7</v>
       </c>
       <c r="H61">
-        <v>40</v>
+        <v>42.5</v>
       </c>
       <c r="I61">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="J61">
         <v>0</v>
@@ -3839,13 +3839,13 @@
         <v>0</v>
       </c>
       <c r="L61">
-        <v>3640</v>
+        <v>2975</v>
       </c>
       <c r="M61" t="str">
-        <v>→ HOLD</v>
+        <v>↑ WEIGHT</v>
       </c>
       <c r="N61" t="str">
-        <v>13@RIR0 on track</v>
+        <v>Hit 20@RIR0 = top of range → +2.5 kg</v>
       </c>
       <c r="O61" t="str">
         <v/>
@@ -3886,7 +3886,7 @@
         <v>35</v>
       </c>
       <c r="I62">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="J62">
         <v>3</v>
@@ -3895,7 +3895,7 @@
         <v>3</v>
       </c>
       <c r="L62">
-        <v>840</v>
+        <v>1050</v>
       </c>
       <c r="M62" t="str">
         <v>First session</v>
@@ -3942,7 +3942,7 @@
         <v>35</v>
       </c>
       <c r="I63">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="J63">
         <v>2</v>
@@ -3951,7 +3951,7 @@
         <v>2</v>
       </c>
       <c r="L63">
-        <v>1260</v>
+        <v>1540</v>
       </c>
       <c r="M63" t="str">
         <v>+1 REP</v>
@@ -3998,7 +3998,7 @@
         <v>35</v>
       </c>
       <c r="I64">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="J64">
         <v>1</v>
@@ -4007,7 +4007,7 @@
         <v>1</v>
       </c>
       <c r="L64">
-        <v>1750</v>
+        <v>2100</v>
       </c>
       <c r="M64" t="str">
         <v>+1 REP</v>
@@ -4054,7 +4054,7 @@
         <v>35</v>
       </c>
       <c r="I65">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="J65">
         <v>0</v>
@@ -4063,13 +4063,13 @@
         <v>0</v>
       </c>
       <c r="L65">
-        <v>2310</v>
+        <v>2520</v>
       </c>
       <c r="M65" t="str">
-        <v>+1 REP</v>
+        <v>→ HOLD</v>
       </c>
       <c r="N65" t="str">
-        <v>RIR 1 &gt; target 0 → +1 rep</v>
+        <v>12@RIR1 on track</v>
       </c>
       <c r="O65" t="str">
         <v/>
@@ -4107,10 +4107,10 @@
         <v>5</v>
       </c>
       <c r="H66">
-        <v>32.5</v>
+        <v>35</v>
       </c>
       <c r="I66">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="J66">
         <v>0</v>
@@ -4119,13 +4119,13 @@
         <v>0</v>
       </c>
       <c r="L66">
-        <v>1787.5</v>
+        <v>1400</v>
       </c>
       <c r="M66" t="str">
-        <v>→ HOLD</v>
+        <v>↑ WEIGHT</v>
       </c>
       <c r="N66" t="str">
-        <v>11@RIR0 on track</v>
+        <v>Hit 12@RIR0 = top of range → +2.5 kg</v>
       </c>
       <c r="O66" t="str">
         <v/>
@@ -4166,7 +4166,7 @@
         <v>45</v>
       </c>
       <c r="I67">
-        <v>12</v>
+        <v>18</v>
       </c>
       <c r="J67">
         <v>3</v>
@@ -4175,7 +4175,7 @@
         <v>3</v>
       </c>
       <c r="L67">
-        <v>1620</v>
+        <v>2430</v>
       </c>
       <c r="M67" t="str">
         <v>First session</v>
@@ -4222,7 +4222,7 @@
         <v>45</v>
       </c>
       <c r="I68">
-        <v>13</v>
+        <v>19</v>
       </c>
       <c r="J68">
         <v>2</v>
@@ -4231,7 +4231,7 @@
         <v>2</v>
       </c>
       <c r="L68">
-        <v>2340</v>
+        <v>3420</v>
       </c>
       <c r="M68" t="str">
         <v>+1 REP</v>
@@ -4278,7 +4278,7 @@
         <v>45</v>
       </c>
       <c r="I69">
-        <v>14</v>
+        <v>20</v>
       </c>
       <c r="J69">
         <v>1</v>
@@ -4287,7 +4287,7 @@
         <v>1</v>
       </c>
       <c r="L69">
-        <v>3150</v>
+        <v>4500</v>
       </c>
       <c r="M69" t="str">
         <v>+1 REP</v>
@@ -4334,7 +4334,7 @@
         <v>45</v>
       </c>
       <c r="I70">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="J70">
         <v>0</v>
@@ -4343,13 +4343,13 @@
         <v>0</v>
       </c>
       <c r="L70">
-        <v>4050</v>
+        <v>5400</v>
       </c>
       <c r="M70" t="str">
-        <v>+1 REP</v>
+        <v>→ HOLD</v>
       </c>
       <c r="N70" t="str">
-        <v>RIR 1 &gt; target 0 → +1 rep</v>
+        <v>20@RIR1 on track</v>
       </c>
       <c r="O70" t="str">
         <v/>
@@ -4387,10 +4387,10 @@
         <v>5</v>
       </c>
       <c r="H71">
-        <v>42.5</v>
+        <v>45</v>
       </c>
       <c r="I71">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="J71">
         <v>0</v>
@@ -4399,13 +4399,13 @@
         <v>0</v>
       </c>
       <c r="L71">
-        <v>3187.5</v>
+        <v>2700</v>
       </c>
       <c r="M71" t="str">
-        <v>→ HOLD</v>
+        <v>↑ WEIGHT</v>
       </c>
       <c r="N71" t="str">
-        <v>15@RIR0 on track</v>
+        <v>Hit 20@RIR0 = top of range → +2.5 kg</v>
       </c>
       <c r="O71" t="str">
         <v/>
@@ -4446,7 +4446,7 @@
         <v>40</v>
       </c>
       <c r="I72">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="J72">
         <v>3</v>
@@ -4455,7 +4455,7 @@
         <v>3</v>
       </c>
       <c r="L72">
-        <v>1200</v>
+        <v>1560</v>
       </c>
       <c r="M72" t="str">
         <v>First session</v>
@@ -4502,7 +4502,7 @@
         <v>40</v>
       </c>
       <c r="I73">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="J73">
         <v>2</v>
@@ -4511,7 +4511,7 @@
         <v>2</v>
       </c>
       <c r="L73">
-        <v>1760</v>
+        <v>2240</v>
       </c>
       <c r="M73" t="str">
         <v>+1 REP</v>
@@ -4558,7 +4558,7 @@
         <v>40</v>
       </c>
       <c r="I74">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="J74">
         <v>1</v>
@@ -4567,7 +4567,7 @@
         <v>1</v>
       </c>
       <c r="L74">
-        <v>2400</v>
+        <v>3000</v>
       </c>
       <c r="M74" t="str">
         <v>+1 REP</v>
@@ -4614,7 +4614,7 @@
         <v>40</v>
       </c>
       <c r="I75">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="J75">
         <v>0</v>
@@ -4623,13 +4623,13 @@
         <v>0</v>
       </c>
       <c r="L75">
-        <v>3120</v>
+        <v>3600</v>
       </c>
       <c r="M75" t="str">
-        <v>+1 REP</v>
+        <v>→ HOLD</v>
       </c>
       <c r="N75" t="str">
-        <v>RIR 1 &gt; target 0 → +1 rep</v>
+        <v>15@RIR1 on track</v>
       </c>
       <c r="O75" t="str">
         <v/>
@@ -4667,10 +4667,10 @@
         <v>6</v>
       </c>
       <c r="H76">
-        <v>40</v>
+        <v>42.5</v>
       </c>
       <c r="I76">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="J76">
         <v>0</v>
@@ -4679,13 +4679,13 @@
         <v>0</v>
       </c>
       <c r="L76">
-        <v>3120</v>
+        <v>2550</v>
       </c>
       <c r="M76" t="str">
-        <v>→ HOLD</v>
+        <v>↑ WEIGHT</v>
       </c>
       <c r="N76" t="str">
-        <v>13@RIR0 on track</v>
+        <v>Hit 15@RIR0 = top of range → +2.5 kg</v>
       </c>
       <c r="O76" t="str">
         <v/>
@@ -4726,7 +4726,7 @@
         <v>20</v>
       </c>
       <c r="I77">
-        <v>12</v>
+        <v>18</v>
       </c>
       <c r="J77">
         <v>3</v>
@@ -4735,7 +4735,7 @@
         <v>3</v>
       </c>
       <c r="L77">
-        <v>720</v>
+        <v>1080</v>
       </c>
       <c r="M77" t="str">
         <v>First session</v>
@@ -4782,7 +4782,7 @@
         <v>20</v>
       </c>
       <c r="I78">
-        <v>13</v>
+        <v>19</v>
       </c>
       <c r="J78">
         <v>2</v>
@@ -4791,7 +4791,7 @@
         <v>2</v>
       </c>
       <c r="L78">
-        <v>1040</v>
+        <v>1520</v>
       </c>
       <c r="M78" t="str">
         <v>+1 REP</v>
@@ -4838,7 +4838,7 @@
         <v>20</v>
       </c>
       <c r="I79">
-        <v>14</v>
+        <v>20</v>
       </c>
       <c r="J79">
         <v>1</v>
@@ -4847,7 +4847,7 @@
         <v>1</v>
       </c>
       <c r="L79">
-        <v>1400</v>
+        <v>2000</v>
       </c>
       <c r="M79" t="str">
         <v>+1 REP</v>
@@ -4894,7 +4894,7 @@
         <v>20</v>
       </c>
       <c r="I80">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="J80">
         <v>0</v>
@@ -4903,13 +4903,13 @@
         <v>0</v>
       </c>
       <c r="L80">
-        <v>1800</v>
+        <v>2400</v>
       </c>
       <c r="M80" t="str">
-        <v>+1 REP</v>
+        <v>→ HOLD</v>
       </c>
       <c r="N80" t="str">
-        <v>RIR 1 &gt; target 0 → +1 rep</v>
+        <v>20@RIR1 on track</v>
       </c>
       <c r="O80" t="str">
         <v/>
@@ -4947,10 +4947,10 @@
         <v>6</v>
       </c>
       <c r="H81">
-        <v>20</v>
+        <v>22.5</v>
       </c>
       <c r="I81">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="J81">
         <v>0</v>
@@ -4959,13 +4959,13 @@
         <v>0</v>
       </c>
       <c r="L81">
-        <v>1800</v>
+        <v>1620</v>
       </c>
       <c r="M81" t="str">
-        <v>→ HOLD</v>
+        <v>↑ WEIGHT</v>
       </c>
       <c r="N81" t="str">
-        <v>15@RIR0 on track</v>
+        <v>Hit 20@RIR0 = top of range → +2.5 kg</v>
       </c>
       <c r="O81" t="str">
         <v/>
@@ -5006,7 +5006,7 @@
         <v>50</v>
       </c>
       <c r="I82">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="J82">
         <v>3</v>
@@ -5015,7 +5015,7 @@
         <v>3</v>
       </c>
       <c r="L82">
-        <v>1200</v>
+        <v>1500</v>
       </c>
       <c r="M82" t="str">
         <v>First session</v>
@@ -5062,7 +5062,7 @@
         <v>50</v>
       </c>
       <c r="I83">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="J83">
         <v>2</v>
@@ -5071,7 +5071,7 @@
         <v>2</v>
       </c>
       <c r="L83">
-        <v>1800</v>
+        <v>2200</v>
       </c>
       <c r="M83" t="str">
         <v>+1 REP</v>
@@ -5118,7 +5118,7 @@
         <v>50</v>
       </c>
       <c r="I84">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="J84">
         <v>1</v>
@@ -5127,7 +5127,7 @@
         <v>1</v>
       </c>
       <c r="L84">
-        <v>2500</v>
+        <v>3000</v>
       </c>
       <c r="M84" t="str">
         <v>+1 REP</v>
@@ -5174,7 +5174,7 @@
         <v>50</v>
       </c>
       <c r="I85">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="J85">
         <v>0</v>
@@ -5183,13 +5183,13 @@
         <v>0</v>
       </c>
       <c r="L85">
-        <v>3300</v>
+        <v>3600</v>
       </c>
       <c r="M85" t="str">
-        <v>+1 REP</v>
+        <v>→ HOLD</v>
       </c>
       <c r="N85" t="str">
-        <v>RIR 1 &gt; target 0 → +1 rep</v>
+        <v>12@RIR1 on track</v>
       </c>
       <c r="O85" t="str">
         <v/>
@@ -5227,10 +5227,10 @@
         <v>4</v>
       </c>
       <c r="H86">
-        <v>45</v>
+        <v>47.5</v>
       </c>
       <c r="I86">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="J86">
         <v>0</v>
@@ -5239,13 +5239,13 @@
         <v>0</v>
       </c>
       <c r="L86">
-        <v>1980</v>
+        <v>1520</v>
       </c>
       <c r="M86" t="str">
-        <v>→ HOLD</v>
+        <v>↑ WEIGHT</v>
       </c>
       <c r="N86" t="str">
-        <v>11@RIR0 on track</v>
+        <v>Hit 12@RIR0 = top of range → +2.5 kg</v>
       </c>
       <c r="O86" t="str">
         <v/>
@@ -5286,7 +5286,7 @@
         <v>25</v>
       </c>
       <c r="I87">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="J87">
         <v>3</v>
@@ -5295,7 +5295,7 @@
         <v>3</v>
       </c>
       <c r="L87">
-        <v>750</v>
+        <v>975</v>
       </c>
       <c r="M87" t="str">
         <v>First session</v>
@@ -5342,7 +5342,7 @@
         <v>25</v>
       </c>
       <c r="I88">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="J88">
         <v>2</v>
@@ -5351,7 +5351,7 @@
         <v>2</v>
       </c>
       <c r="L88">
-        <v>1100</v>
+        <v>1400</v>
       </c>
       <c r="M88" t="str">
         <v>+1 REP</v>
@@ -5398,7 +5398,7 @@
         <v>25</v>
       </c>
       <c r="I89">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="J89">
         <v>1</v>
@@ -5407,7 +5407,7 @@
         <v>1</v>
       </c>
       <c r="L89">
-        <v>1500</v>
+        <v>1875</v>
       </c>
       <c r="M89" t="str">
         <v>+1 REP</v>
@@ -5454,7 +5454,7 @@
         <v>25</v>
       </c>
       <c r="I90">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="J90">
         <v>0</v>
@@ -5463,13 +5463,13 @@
         <v>0</v>
       </c>
       <c r="L90">
-        <v>1950</v>
+        <v>2250</v>
       </c>
       <c r="M90" t="str">
-        <v>+1 REP</v>
+        <v>→ HOLD</v>
       </c>
       <c r="N90" t="str">
-        <v>RIR 1 &gt; target 0 → +1 rep</v>
+        <v>15@RIR1 on track</v>
       </c>
       <c r="O90" t="str">
         <v/>
@@ -5507,10 +5507,10 @@
         <v>4</v>
       </c>
       <c r="H91">
-        <v>22.5</v>
+        <v>25</v>
       </c>
       <c r="I91">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="J91">
         <v>0</v>
@@ -5519,13 +5519,13 @@
         <v>0</v>
       </c>
       <c r="L91">
-        <v>1170</v>
+        <v>1000</v>
       </c>
       <c r="M91" t="str">
-        <v>→ HOLD</v>
+        <v>↑ WEIGHT</v>
       </c>
       <c r="N91" t="str">
-        <v>13@RIR0 on track</v>
+        <v>Hit 15@RIR0 = top of range → +2.5 kg</v>
       </c>
       <c r="O91" t="str">
         <v/>
@@ -5566,7 +5566,7 @@
         <v>30</v>
       </c>
       <c r="I92">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="J92">
         <v>3</v>
@@ -5575,7 +5575,7 @@
         <v>3</v>
       </c>
       <c r="L92">
-        <v>720</v>
+        <v>900</v>
       </c>
       <c r="M92" t="str">
         <v>First session</v>
@@ -5622,7 +5622,7 @@
         <v>30</v>
       </c>
       <c r="I93">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="J93">
         <v>2</v>
@@ -5631,7 +5631,7 @@
         <v>2</v>
       </c>
       <c r="L93">
-        <v>1080</v>
+        <v>1320</v>
       </c>
       <c r="M93" t="str">
         <v>+1 REP</v>
@@ -5678,7 +5678,7 @@
         <v>30</v>
       </c>
       <c r="I94">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="J94">
         <v>1</v>
@@ -5687,7 +5687,7 @@
         <v>1</v>
       </c>
       <c r="L94">
-        <v>1500</v>
+        <v>1800</v>
       </c>
       <c r="M94" t="str">
         <v>+1 REP</v>
@@ -5734,7 +5734,7 @@
         <v>30</v>
       </c>
       <c r="I95">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="J95">
         <v>0</v>
@@ -5743,13 +5743,13 @@
         <v>0</v>
       </c>
       <c r="L95">
-        <v>1980</v>
+        <v>2160</v>
       </c>
       <c r="M95" t="str">
-        <v>+1 REP</v>
+        <v>→ HOLD</v>
       </c>
       <c r="N95" t="str">
-        <v>RIR 1 &gt; target 0 → +1 rep</v>
+        <v>12@RIR1 on track</v>
       </c>
       <c r="O95" t="str">
         <v/>
@@ -5787,10 +5787,10 @@
         <v>4</v>
       </c>
       <c r="H96">
-        <v>27.5</v>
+        <v>30</v>
       </c>
       <c r="I96">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="J96">
         <v>0</v>
@@ -5799,13 +5799,13 @@
         <v>0</v>
       </c>
       <c r="L96">
-        <v>1210</v>
+        <v>960</v>
       </c>
       <c r="M96" t="str">
-        <v>→ HOLD</v>
+        <v>↑ WEIGHT</v>
       </c>
       <c r="N96" t="str">
-        <v>11@RIR0 on track</v>
+        <v>Hit 12@RIR0 = top of range → +2.5 kg</v>
       </c>
       <c r="O96" t="str">
         <v/>
@@ -5846,7 +5846,7 @@
         <v>12.5</v>
       </c>
       <c r="I97">
-        <v>12</v>
+        <v>18</v>
       </c>
       <c r="J97">
         <v>3</v>
@@ -5855,7 +5855,7 @@
         <v>3</v>
       </c>
       <c r="L97">
-        <v>300</v>
+        <v>450</v>
       </c>
       <c r="M97" t="str">
         <v>First session</v>
@@ -5902,7 +5902,7 @@
         <v>12.5</v>
       </c>
       <c r="I98">
-        <v>13</v>
+        <v>19</v>
       </c>
       <c r="J98">
         <v>2</v>
@@ -5911,7 +5911,7 @@
         <v>2</v>
       </c>
       <c r="L98">
-        <v>487.5</v>
+        <v>712.5</v>
       </c>
       <c r="M98" t="str">
         <v>+1 REP</v>
@@ -5958,7 +5958,7 @@
         <v>12.5</v>
       </c>
       <c r="I99">
-        <v>14</v>
+        <v>20</v>
       </c>
       <c r="J99">
         <v>1</v>
@@ -5967,7 +5967,7 @@
         <v>1</v>
       </c>
       <c r="L99">
-        <v>700</v>
+        <v>1000</v>
       </c>
       <c r="M99" t="str">
         <v>+1 REP</v>
@@ -6014,7 +6014,7 @@
         <v>12.5</v>
       </c>
       <c r="I100">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="J100">
         <v>0</v>
@@ -6023,13 +6023,13 @@
         <v>0</v>
       </c>
       <c r="L100">
-        <v>937.5</v>
+        <v>1250</v>
       </c>
       <c r="M100" t="str">
-        <v>+1 REP</v>
+        <v>→ HOLD</v>
       </c>
       <c r="N100" t="str">
-        <v>RIR 1 &gt; target 0 → +1 rep</v>
+        <v>20@RIR1 on track</v>
       </c>
       <c r="O100" t="str">
         <v/>
@@ -6070,7 +6070,7 @@
         <v>12.5</v>
       </c>
       <c r="I101">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="J101">
         <v>0</v>
@@ -6079,13 +6079,13 @@
         <v>0</v>
       </c>
       <c r="L101">
-        <v>562.5</v>
+        <v>450</v>
       </c>
       <c r="M101" t="str">
-        <v>→ HOLD</v>
+        <v>↑ WEIGHT</v>
       </c>
       <c r="N101" t="str">
-        <v>15@RIR0 on track</v>
+        <v>Hit 20@RIR0 = top of range → +2.5 kg</v>
       </c>
       <c r="O101" t="str">
         <v/>
@@ -6126,7 +6126,7 @@
         <v>80</v>
       </c>
       <c r="I102">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="J102">
         <v>3</v>
@@ -6135,7 +6135,7 @@
         <v>3</v>
       </c>
       <c r="L102">
-        <v>1920</v>
+        <v>2400</v>
       </c>
       <c r="M102" t="str">
         <v>First session</v>
@@ -6182,7 +6182,7 @@
         <v>80</v>
       </c>
       <c r="I103">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="J103">
         <v>2</v>
@@ -6191,7 +6191,7 @@
         <v>2</v>
       </c>
       <c r="L103">
-        <v>2880</v>
+        <v>3520</v>
       </c>
       <c r="M103" t="str">
         <v>+1 REP</v>
@@ -6238,7 +6238,7 @@
         <v>80</v>
       </c>
       <c r="I104">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="J104">
         <v>1</v>
@@ -6247,7 +6247,7 @@
         <v>1</v>
       </c>
       <c r="L104">
-        <v>4000</v>
+        <v>4800</v>
       </c>
       <c r="M104" t="str">
         <v>+1 REP</v>
@@ -6294,7 +6294,7 @@
         <v>72.5</v>
       </c>
       <c r="I105">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="J105">
         <v>0</v>
@@ -6303,13 +6303,13 @@
         <v>0</v>
       </c>
       <c r="L105">
-        <v>3190</v>
+        <v>3480</v>
       </c>
       <c r="M105" t="str">
-        <v>+1 REP</v>
+        <v>→ HOLD</v>
       </c>
       <c r="N105" t="str">
-        <v>RIR 1 &gt; target 0 → +1 rep</v>
+        <v>12@RIR1 on track</v>
       </c>
       <c r="O105" t="str">
         <v/>
@@ -6347,10 +6347,10 @@
         <v>4</v>
       </c>
       <c r="H106">
-        <v>65</v>
+        <v>67.5</v>
       </c>
       <c r="I106">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="J106">
         <v>0</v>
@@ -6359,13 +6359,13 @@
         <v>0</v>
       </c>
       <c r="L106">
-        <v>2860</v>
+        <v>2160</v>
       </c>
       <c r="M106" t="str">
-        <v>→ HOLD</v>
+        <v>↑ WEIGHT</v>
       </c>
       <c r="N106" t="str">
-        <v>11@RIR0 on track</v>
+        <v>Hit 12@RIR0 = top of range → +2.5 kg</v>
       </c>
       <c r="O106" t="str">
         <v/>
@@ -6406,7 +6406,7 @@
         <v>40</v>
       </c>
       <c r="I107">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="J107">
         <v>3</v>
@@ -6415,7 +6415,7 @@
         <v>3</v>
       </c>
       <c r="L107">
-        <v>1200</v>
+        <v>1560</v>
       </c>
       <c r="M107" t="str">
         <v>First session</v>
@@ -6462,7 +6462,7 @@
         <v>40</v>
       </c>
       <c r="I108">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="J108">
         <v>2</v>
@@ -6471,7 +6471,7 @@
         <v>2</v>
       </c>
       <c r="L108">
-        <v>1760</v>
+        <v>2240</v>
       </c>
       <c r="M108" t="str">
         <v>+1 REP</v>
@@ -6518,7 +6518,7 @@
         <v>40</v>
       </c>
       <c r="I109">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="J109">
         <v>1</v>
@@ -6527,7 +6527,7 @@
         <v>1</v>
       </c>
       <c r="L109">
-        <v>2400</v>
+        <v>3000</v>
       </c>
       <c r="M109" t="str">
         <v>+1 REP</v>
@@ -6574,7 +6574,7 @@
         <v>40</v>
       </c>
       <c r="I110">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="J110">
         <v>0</v>
@@ -6583,13 +6583,13 @@
         <v>0</v>
       </c>
       <c r="L110">
-        <v>3120</v>
+        <v>3600</v>
       </c>
       <c r="M110" t="str">
-        <v>+1 REP</v>
+        <v>→ HOLD</v>
       </c>
       <c r="N110" t="str">
-        <v>RIR 1 &gt; target 0 → +1 rep</v>
+        <v>15@RIR1 on track</v>
       </c>
       <c r="O110" t="str">
         <v/>
@@ -6627,10 +6627,10 @@
         <v>4</v>
       </c>
       <c r="H111">
-        <v>35</v>
+        <v>37.5</v>
       </c>
       <c r="I111">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="J111">
         <v>0</v>
@@ -6639,13 +6639,13 @@
         <v>0</v>
       </c>
       <c r="L111">
-        <v>1820</v>
+        <v>1500</v>
       </c>
       <c r="M111" t="str">
-        <v>→ HOLD</v>
+        <v>↑ WEIGHT</v>
       </c>
       <c r="N111" t="str">
-        <v>13@RIR0 on track</v>
+        <v>Hit 15@RIR0 = top of range → +2.5 kg</v>
       </c>
       <c r="O111" t="str">
         <v/>
@@ -6686,7 +6686,7 @@
         <v>80</v>
       </c>
       <c r="I112">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="J112">
         <v>3</v>
@@ -6695,7 +6695,7 @@
         <v>3</v>
       </c>
       <c r="L112">
-        <v>1920</v>
+        <v>2400</v>
       </c>
       <c r="M112" t="str">
         <v>First session</v>
@@ -6742,7 +6742,7 @@
         <v>80</v>
       </c>
       <c r="I113">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="J113">
         <v>2</v>
@@ -6751,7 +6751,7 @@
         <v>2</v>
       </c>
       <c r="L113">
-        <v>2880</v>
+        <v>3520</v>
       </c>
       <c r="M113" t="str">
         <v>+1 REP</v>
@@ -6798,7 +6798,7 @@
         <v>80</v>
       </c>
       <c r="I114">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="J114">
         <v>1</v>
@@ -6807,7 +6807,7 @@
         <v>1</v>
       </c>
       <c r="L114">
-        <v>4000</v>
+        <v>4800</v>
       </c>
       <c r="M114" t="str">
         <v>+1 REP</v>
@@ -6854,7 +6854,7 @@
         <v>80</v>
       </c>
       <c r="I115">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="J115">
         <v>0</v>
@@ -6863,13 +6863,13 @@
         <v>0</v>
       </c>
       <c r="L115">
-        <v>5280</v>
+        <v>5760</v>
       </c>
       <c r="M115" t="str">
-        <v>+1 REP</v>
+        <v>→ HOLD</v>
       </c>
       <c r="N115" t="str">
-        <v>RIR 1 &gt; target 0 → +1 rep</v>
+        <v>12@RIR1 on track</v>
       </c>
       <c r="O115" t="str">
         <v/>
@@ -6907,10 +6907,10 @@
         <v>6</v>
       </c>
       <c r="H116">
-        <v>80</v>
+        <v>82.5</v>
       </c>
       <c r="I116">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="J116">
         <v>0</v>
@@ -6919,13 +6919,13 @@
         <v>0</v>
       </c>
       <c r="L116">
-        <v>5280</v>
+        <v>3960</v>
       </c>
       <c r="M116" t="str">
-        <v>→ HOLD</v>
+        <v>↑ WEIGHT</v>
       </c>
       <c r="N116" t="str">
-        <v>11@RIR0 on track</v>
+        <v>Hit 12@RIR0 = top of range → +2.5 kg</v>
       </c>
       <c r="O116" t="str">
         <v/>
@@ -6966,7 +6966,7 @@
         <v>30</v>
       </c>
       <c r="I117">
-        <v>10</v>
+        <v>18</v>
       </c>
       <c r="J117">
         <v>3</v>
@@ -6975,7 +6975,7 @@
         <v>3</v>
       </c>
       <c r="L117">
-        <v>900</v>
+        <v>1620</v>
       </c>
       <c r="M117" t="str">
         <v>First session</v>
@@ -7022,7 +7022,7 @@
         <v>30</v>
       </c>
       <c r="I118">
-        <v>11</v>
+        <v>19</v>
       </c>
       <c r="J118">
         <v>2</v>
@@ -7031,7 +7031,7 @@
         <v>2</v>
       </c>
       <c r="L118">
-        <v>1320</v>
+        <v>2280</v>
       </c>
       <c r="M118" t="str">
         <v>+1 REP</v>
@@ -7078,7 +7078,7 @@
         <v>30</v>
       </c>
       <c r="I119">
-        <v>12</v>
+        <v>20</v>
       </c>
       <c r="J119">
         <v>1</v>
@@ -7087,7 +7087,7 @@
         <v>1</v>
       </c>
       <c r="L119">
-        <v>1800</v>
+        <v>3000</v>
       </c>
       <c r="M119" t="str">
         <v>+1 REP</v>
@@ -7134,7 +7134,7 @@
         <v>30</v>
       </c>
       <c r="I120">
-        <v>13</v>
+        <v>20</v>
       </c>
       <c r="J120">
         <v>0</v>
@@ -7143,13 +7143,13 @@
         <v>0</v>
       </c>
       <c r="L120">
-        <v>2340</v>
+        <v>3600</v>
       </c>
       <c r="M120" t="str">
-        <v>+1 REP</v>
+        <v>→ HOLD</v>
       </c>
       <c r="N120" t="str">
-        <v>RIR 1 &gt; target 0 → +1 rep</v>
+        <v>20@RIR1 on track</v>
       </c>
       <c r="O120" t="str">
         <v/>
@@ -7187,10 +7187,10 @@
         <v>6</v>
       </c>
       <c r="H121">
-        <v>30</v>
+        <v>32.5</v>
       </c>
       <c r="I121">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="J121">
         <v>0</v>
@@ -7199,13 +7199,13 @@
         <v>0</v>
       </c>
       <c r="L121">
-        <v>2340</v>
+        <v>1950</v>
       </c>
       <c r="M121" t="str">
-        <v>→ HOLD</v>
+        <v>↑ WEIGHT</v>
       </c>
       <c r="N121" t="str">
-        <v>13@RIR0 on track</v>
+        <v>Hit 20@RIR0 = top of range → +2.5 kg</v>
       </c>
       <c r="O121" t="str">
         <v/>
@@ -7297,13 +7297,13 @@
         <v>120</v>
       </c>
       <c r="E2">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="F2">
         <v>3</v>
       </c>
       <c r="G2">
-        <v>2880</v>
+        <v>3600</v>
       </c>
       <c r="H2" t="str">
         <v>First session</v>
@@ -7335,13 +7335,13 @@
         <v>120</v>
       </c>
       <c r="E3">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="F3">
         <v>2</v>
       </c>
       <c r="G3">
-        <v>4320</v>
+        <v>5280</v>
       </c>
       <c r="H3" t="str">
         <v>+1 REP</v>
@@ -7373,13 +7373,13 @@
         <v>120</v>
       </c>
       <c r="E4">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="F4">
         <v>1</v>
       </c>
       <c r="G4">
-        <v>6000</v>
+        <v>7200</v>
       </c>
       <c r="H4" t="str">
         <v>+1 REP</v>
@@ -7411,19 +7411,19 @@
         <v>107.5</v>
       </c>
       <c r="E5">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="F5">
         <v>0</v>
       </c>
       <c r="G5">
-        <v>4730</v>
+        <v>5160</v>
       </c>
       <c r="H5" t="str">
-        <v>+1 REP</v>
+        <v>→ HOLD</v>
       </c>
       <c r="I5" t="str">
-        <v>RIR 1 &gt; target 0 → +1 rep</v>
+        <v>12@RIR1 on track</v>
       </c>
       <c r="J5" t="str">
         <v/>
@@ -7446,22 +7446,22 @@
         <v>4</v>
       </c>
       <c r="D6">
-        <v>97.5</v>
+        <v>100</v>
       </c>
       <c r="E6">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="F6">
         <v>0</v>
       </c>
       <c r="G6">
-        <v>4290</v>
+        <v>3200</v>
       </c>
       <c r="H6" t="str">
-        <v>→ HOLD</v>
+        <v>↑ WEIGHT</v>
       </c>
       <c r="I6" t="str">
-        <v>11@RIR0 on track</v>
+        <v>Hit 12@RIR0 = top of range → +2.5 kg</v>
       </c>
       <c r="J6" t="str">
         <v/>
@@ -7550,13 +7550,13 @@
         <v>50</v>
       </c>
       <c r="E2">
-        <v>12</v>
+        <v>18</v>
       </c>
       <c r="F2">
         <v>3</v>
       </c>
       <c r="G2">
-        <v>1800</v>
+        <v>2700</v>
       </c>
       <c r="H2" t="str">
         <v>First session</v>
@@ -7588,13 +7588,13 @@
         <v>50</v>
       </c>
       <c r="E3">
-        <v>13</v>
+        <v>19</v>
       </c>
       <c r="F3">
         <v>2</v>
       </c>
       <c r="G3">
-        <v>2600</v>
+        <v>3800</v>
       </c>
       <c r="H3" t="str">
         <v>+1 REP</v>
@@ -7626,13 +7626,13 @@
         <v>50</v>
       </c>
       <c r="E4">
-        <v>14</v>
+        <v>20</v>
       </c>
       <c r="F4">
         <v>1</v>
       </c>
       <c r="G4">
-        <v>3500</v>
+        <v>5000</v>
       </c>
       <c r="H4" t="str">
         <v>+1 REP</v>
@@ -7664,19 +7664,19 @@
         <v>45</v>
       </c>
       <c r="E5">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="F5">
         <v>0</v>
       </c>
       <c r="G5">
-        <v>2700</v>
+        <v>3600</v>
       </c>
       <c r="H5" t="str">
-        <v>+1 REP</v>
+        <v>→ HOLD</v>
       </c>
       <c r="I5" t="str">
-        <v>RIR 1 &gt; target 0 → +1 rep</v>
+        <v>20@RIR1 on track</v>
       </c>
       <c r="J5" t="str">
         <v/>
@@ -7699,22 +7699,22 @@
         <v>4</v>
       </c>
       <c r="D6">
-        <v>40</v>
+        <v>42.5</v>
       </c>
       <c r="E6">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="F6">
         <v>0</v>
       </c>
       <c r="G6">
-        <v>2400</v>
+        <v>2040</v>
       </c>
       <c r="H6" t="str">
-        <v>→ HOLD</v>
+        <v>↑ WEIGHT</v>
       </c>
       <c r="I6" t="str">
-        <v>15@RIR0 on track</v>
+        <v>Hit 20@RIR0 = top of range → +2.5 kg</v>
       </c>
       <c r="J6" t="str">
         <v/>
@@ -7803,13 +7803,13 @@
         <v>60</v>
       </c>
       <c r="E2">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="F2">
         <v>3</v>
       </c>
       <c r="G2">
-        <v>1440</v>
+        <v>1800</v>
       </c>
       <c r="H2" t="str">
         <v>First session</v>
@@ -7841,13 +7841,13 @@
         <v>60</v>
       </c>
       <c r="E3">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="F3">
         <v>2</v>
       </c>
       <c r="G3">
-        <v>2160</v>
+        <v>2640</v>
       </c>
       <c r="H3" t="str">
         <v>+1 REP</v>
@@ -7879,13 +7879,13 @@
         <v>60</v>
       </c>
       <c r="E4">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="F4">
         <v>1</v>
       </c>
       <c r="G4">
-        <v>3000</v>
+        <v>3600</v>
       </c>
       <c r="H4" t="str">
         <v>+1 REP</v>
@@ -7917,19 +7917,19 @@
         <v>60</v>
       </c>
       <c r="E5">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="F5">
         <v>0</v>
       </c>
       <c r="G5">
-        <v>3960</v>
+        <v>4320</v>
       </c>
       <c r="H5" t="str">
-        <v>+1 REP</v>
+        <v>→ HOLD</v>
       </c>
       <c r="I5" t="str">
-        <v>RIR 1 &gt; target 0 → +1 rep</v>
+        <v>12@RIR1 on track</v>
       </c>
       <c r="J5" t="str">
         <v/>
@@ -7952,22 +7952,22 @@
         <v>4</v>
       </c>
       <c r="D6">
-        <v>55</v>
+        <v>57.5</v>
       </c>
       <c r="E6">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="F6">
         <v>0</v>
       </c>
       <c r="G6">
-        <v>2420</v>
+        <v>1840</v>
       </c>
       <c r="H6" t="str">
-        <v>→ HOLD</v>
+        <v>↑ WEIGHT</v>
       </c>
       <c r="I6" t="str">
-        <v>11@RIR0 on track</v>
+        <v>Hit 12@RIR0 = top of range → +2.5 kg</v>
       </c>
       <c r="J6" t="str">
         <v/>
@@ -8056,13 +8056,13 @@
         <v>40</v>
       </c>
       <c r="E2">
-        <v>10</v>
+        <v>18</v>
       </c>
       <c r="F2">
         <v>3</v>
       </c>
       <c r="G2">
-        <v>1600</v>
+        <v>2880</v>
       </c>
       <c r="H2" t="str">
         <v>First session</v>
@@ -8094,13 +8094,13 @@
         <v>40</v>
       </c>
       <c r="E3">
-        <v>11</v>
+        <v>19</v>
       </c>
       <c r="F3">
         <v>2</v>
       </c>
       <c r="G3">
-        <v>2200</v>
+        <v>3800</v>
       </c>
       <c r="H3" t="str">
         <v>+1 REP</v>
@@ -8132,13 +8132,13 @@
         <v>40</v>
       </c>
       <c r="E4">
-        <v>12</v>
+        <v>20</v>
       </c>
       <c r="F4">
         <v>1</v>
       </c>
       <c r="G4">
-        <v>2880</v>
+        <v>4800</v>
       </c>
       <c r="H4" t="str">
         <v>+1 REP</v>
@@ -8170,19 +8170,19 @@
         <v>40</v>
       </c>
       <c r="E5">
-        <v>13</v>
+        <v>20</v>
       </c>
       <c r="F5">
         <v>0</v>
       </c>
       <c r="G5">
-        <v>3640</v>
+        <v>5600</v>
       </c>
       <c r="H5" t="str">
-        <v>+1 REP</v>
+        <v>→ HOLD</v>
       </c>
       <c r="I5" t="str">
-        <v>RIR 1 &gt; target 0 → +1 rep</v>
+        <v>20@RIR1 on track</v>
       </c>
       <c r="J5" t="str">
         <v/>
@@ -8205,22 +8205,22 @@
         <v>7</v>
       </c>
       <c r="D6">
-        <v>40</v>
+        <v>42.5</v>
       </c>
       <c r="E6">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="F6">
         <v>0</v>
       </c>
       <c r="G6">
-        <v>3640</v>
+        <v>2975</v>
       </c>
       <c r="H6" t="str">
-        <v>→ HOLD</v>
+        <v>↑ WEIGHT</v>
       </c>
       <c r="I6" t="str">
-        <v>13@RIR0 on track</v>
+        <v>Hit 20@RIR0 = top of range → +2.5 kg</v>
       </c>
       <c r="J6" t="str">
         <v/>
@@ -8309,13 +8309,13 @@
         <v>35</v>
       </c>
       <c r="E2">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="F2">
         <v>3</v>
       </c>
       <c r="G2">
-        <v>840</v>
+        <v>1050</v>
       </c>
       <c r="H2" t="str">
         <v>First session</v>
@@ -8347,13 +8347,13 @@
         <v>35</v>
       </c>
       <c r="E3">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="F3">
         <v>2</v>
       </c>
       <c r="G3">
-        <v>1260</v>
+        <v>1540</v>
       </c>
       <c r="H3" t="str">
         <v>+1 REP</v>
@@ -8385,13 +8385,13 @@
         <v>35</v>
       </c>
       <c r="E4">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="F4">
         <v>1</v>
       </c>
       <c r="G4">
-        <v>1750</v>
+        <v>2100</v>
       </c>
       <c r="H4" t="str">
         <v>+1 REP</v>
@@ -8423,19 +8423,19 @@
         <v>35</v>
       </c>
       <c r="E5">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="F5">
         <v>0</v>
       </c>
       <c r="G5">
-        <v>2310</v>
+        <v>2520</v>
       </c>
       <c r="H5" t="str">
-        <v>+1 REP</v>
+        <v>→ HOLD</v>
       </c>
       <c r="I5" t="str">
-        <v>RIR 1 &gt; target 0 → +1 rep</v>
+        <v>12@RIR1 on track</v>
       </c>
       <c r="J5" t="str">
         <v/>
@@ -8458,22 +8458,22 @@
         <v>5</v>
       </c>
       <c r="D6">
-        <v>32.5</v>
+        <v>35</v>
       </c>
       <c r="E6">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="F6">
         <v>0</v>
       </c>
       <c r="G6">
-        <v>1787.5</v>
+        <v>1400</v>
       </c>
       <c r="H6" t="str">
-        <v>→ HOLD</v>
+        <v>↑ WEIGHT</v>
       </c>
       <c r="I6" t="str">
-        <v>11@RIR0 on track</v>
+        <v>Hit 12@RIR0 = top of range → +2.5 kg</v>
       </c>
       <c r="J6" t="str">
         <v/>
@@ -8562,13 +8562,13 @@
         <v>45</v>
       </c>
       <c r="E2">
-        <v>12</v>
+        <v>18</v>
       </c>
       <c r="F2">
         <v>3</v>
       </c>
       <c r="G2">
-        <v>1620</v>
+        <v>2430</v>
       </c>
       <c r="H2" t="str">
         <v>First session</v>
@@ -8600,13 +8600,13 @@
         <v>45</v>
       </c>
       <c r="E3">
-        <v>13</v>
+        <v>19</v>
       </c>
       <c r="F3">
         <v>2</v>
       </c>
       <c r="G3">
-        <v>2340</v>
+        <v>3420</v>
       </c>
       <c r="H3" t="str">
         <v>+1 REP</v>
@@ -8638,13 +8638,13 @@
         <v>45</v>
       </c>
       <c r="E4">
-        <v>14</v>
+        <v>20</v>
       </c>
       <c r="F4">
         <v>1</v>
       </c>
       <c r="G4">
-        <v>3150</v>
+        <v>4500</v>
       </c>
       <c r="H4" t="str">
         <v>+1 REP</v>
@@ -8676,19 +8676,19 @@
         <v>45</v>
       </c>
       <c r="E5">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="F5">
         <v>0</v>
       </c>
       <c r="G5">
-        <v>4050</v>
+        <v>5400</v>
       </c>
       <c r="H5" t="str">
-        <v>+1 REP</v>
+        <v>→ HOLD</v>
       </c>
       <c r="I5" t="str">
-        <v>RIR 1 &gt; target 0 → +1 rep</v>
+        <v>20@RIR1 on track</v>
       </c>
       <c r="J5" t="str">
         <v/>
@@ -8711,22 +8711,22 @@
         <v>5</v>
       </c>
       <c r="D6">
-        <v>42.5</v>
+        <v>45</v>
       </c>
       <c r="E6">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="F6">
         <v>0</v>
       </c>
       <c r="G6">
-        <v>3187.5</v>
+        <v>2700</v>
       </c>
       <c r="H6" t="str">
-        <v>→ HOLD</v>
+        <v>↑ WEIGHT</v>
       </c>
       <c r="I6" t="str">
-        <v>15@RIR0 on track</v>
+        <v>Hit 20@RIR0 = top of range → +2.5 kg</v>
       </c>
       <c r="J6" t="str">
         <v/>
@@ -8815,13 +8815,13 @@
         <v>40</v>
       </c>
       <c r="E2">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="F2">
         <v>3</v>
       </c>
       <c r="G2">
-        <v>1200</v>
+        <v>1560</v>
       </c>
       <c r="H2" t="str">
         <v>First session</v>
@@ -8853,13 +8853,13 @@
         <v>40</v>
       </c>
       <c r="E3">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="F3">
         <v>2</v>
       </c>
       <c r="G3">
-        <v>1760</v>
+        <v>2240</v>
       </c>
       <c r="H3" t="str">
         <v>+1 REP</v>
@@ -8891,13 +8891,13 @@
         <v>40</v>
       </c>
       <c r="E4">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="F4">
         <v>1</v>
       </c>
       <c r="G4">
-        <v>2400</v>
+        <v>3000</v>
       </c>
       <c r="H4" t="str">
         <v>+1 REP</v>
@@ -8929,19 +8929,19 @@
         <v>40</v>
       </c>
       <c r="E5">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="F5">
         <v>0</v>
       </c>
       <c r="G5">
-        <v>3120</v>
+        <v>3600</v>
       </c>
       <c r="H5" t="str">
-        <v>+1 REP</v>
+        <v>→ HOLD</v>
       </c>
       <c r="I5" t="str">
-        <v>RIR 1 &gt; target 0 → +1 rep</v>
+        <v>15@RIR1 on track</v>
       </c>
       <c r="J5" t="str">
         <v/>
@@ -8964,22 +8964,22 @@
         <v>6</v>
       </c>
       <c r="D6">
-        <v>40</v>
+        <v>42.5</v>
       </c>
       <c r="E6">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="F6">
         <v>0</v>
       </c>
       <c r="G6">
-        <v>3120</v>
+        <v>2550</v>
       </c>
       <c r="H6" t="str">
-        <v>→ HOLD</v>
+        <v>↑ WEIGHT</v>
       </c>
       <c r="I6" t="str">
-        <v>13@RIR0 on track</v>
+        <v>Hit 15@RIR0 = top of range → +2.5 kg</v>
       </c>
       <c r="J6" t="str">
         <v/>
@@ -9068,13 +9068,13 @@
         <v>20</v>
       </c>
       <c r="E2">
-        <v>12</v>
+        <v>18</v>
       </c>
       <c r="F2">
         <v>3</v>
       </c>
       <c r="G2">
-        <v>720</v>
+        <v>1080</v>
       </c>
       <c r="H2" t="str">
         <v>First session</v>
@@ -9106,13 +9106,13 @@
         <v>20</v>
       </c>
       <c r="E3">
-        <v>13</v>
+        <v>19</v>
       </c>
       <c r="F3">
         <v>2</v>
       </c>
       <c r="G3">
-        <v>1040</v>
+        <v>1520</v>
       </c>
       <c r="H3" t="str">
         <v>+1 REP</v>
@@ -9144,13 +9144,13 @@
         <v>20</v>
       </c>
       <c r="E4">
-        <v>14</v>
+        <v>20</v>
       </c>
       <c r="F4">
         <v>1</v>
       </c>
       <c r="G4">
-        <v>1400</v>
+        <v>2000</v>
       </c>
       <c r="H4" t="str">
         <v>+1 REP</v>
@@ -9182,19 +9182,19 @@
         <v>20</v>
       </c>
       <c r="E5">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="F5">
         <v>0</v>
       </c>
       <c r="G5">
-        <v>1800</v>
+        <v>2400</v>
       </c>
       <c r="H5" t="str">
-        <v>+1 REP</v>
+        <v>→ HOLD</v>
       </c>
       <c r="I5" t="str">
-        <v>RIR 1 &gt; target 0 → +1 rep</v>
+        <v>20@RIR1 on track</v>
       </c>
       <c r="J5" t="str">
         <v/>
@@ -9217,22 +9217,22 @@
         <v>6</v>
       </c>
       <c r="D6">
-        <v>20</v>
+        <v>22.5</v>
       </c>
       <c r="E6">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="F6">
         <v>0</v>
       </c>
       <c r="G6">
-        <v>1800</v>
+        <v>1620</v>
       </c>
       <c r="H6" t="str">
-        <v>→ HOLD</v>
+        <v>↑ WEIGHT</v>
       </c>
       <c r="I6" t="str">
-        <v>15@RIR0 on track</v>
+        <v>Hit 20@RIR0 = top of range → +2.5 kg</v>
       </c>
       <c r="J6" t="str">
         <v/>
@@ -9321,13 +9321,13 @@
         <v>50</v>
       </c>
       <c r="E2">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="F2">
         <v>3</v>
       </c>
       <c r="G2">
-        <v>1200</v>
+        <v>1500</v>
       </c>
       <c r="H2" t="str">
         <v>First session</v>
@@ -9359,13 +9359,13 @@
         <v>50</v>
       </c>
       <c r="E3">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="F3">
         <v>2</v>
       </c>
       <c r="G3">
-        <v>1800</v>
+        <v>2200</v>
       </c>
       <c r="H3" t="str">
         <v>+1 REP</v>
@@ -9397,13 +9397,13 @@
         <v>50</v>
       </c>
       <c r="E4">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="F4">
         <v>1</v>
       </c>
       <c r="G4">
-        <v>2500</v>
+        <v>3000</v>
       </c>
       <c r="H4" t="str">
         <v>+1 REP</v>
@@ -9435,19 +9435,19 @@
         <v>50</v>
       </c>
       <c r="E5">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="F5">
         <v>0</v>
       </c>
       <c r="G5">
-        <v>3300</v>
+        <v>3600</v>
       </c>
       <c r="H5" t="str">
-        <v>+1 REP</v>
+        <v>→ HOLD</v>
       </c>
       <c r="I5" t="str">
-        <v>RIR 1 &gt; target 0 → +1 rep</v>
+        <v>12@RIR1 on track</v>
       </c>
       <c r="J5" t="str">
         <v/>
@@ -9470,22 +9470,22 @@
         <v>4</v>
       </c>
       <c r="D6">
-        <v>45</v>
+        <v>47.5</v>
       </c>
       <c r="E6">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="F6">
         <v>0</v>
       </c>
       <c r="G6">
-        <v>1980</v>
+        <v>1520</v>
       </c>
       <c r="H6" t="str">
-        <v>→ HOLD</v>
+        <v>↑ WEIGHT</v>
       </c>
       <c r="I6" t="str">
-        <v>11@RIR0 on track</v>
+        <v>Hit 12@RIR0 = top of range → +2.5 kg</v>
       </c>
       <c r="J6" t="str">
         <v/>
@@ -9574,13 +9574,13 @@
         <v>25</v>
       </c>
       <c r="E2">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="F2">
         <v>3</v>
       </c>
       <c r="G2">
-        <v>750</v>
+        <v>975</v>
       </c>
       <c r="H2" t="str">
         <v>First session</v>
@@ -9612,13 +9612,13 @@
         <v>25</v>
       </c>
       <c r="E3">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="F3">
         <v>2</v>
       </c>
       <c r="G3">
-        <v>1100</v>
+        <v>1400</v>
       </c>
       <c r="H3" t="str">
         <v>+1 REP</v>
@@ -9650,13 +9650,13 @@
         <v>25</v>
       </c>
       <c r="E4">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="F4">
         <v>1</v>
       </c>
       <c r="G4">
-        <v>1500</v>
+        <v>1875</v>
       </c>
       <c r="H4" t="str">
         <v>+1 REP</v>
@@ -9688,19 +9688,19 @@
         <v>25</v>
       </c>
       <c r="E5">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="F5">
         <v>0</v>
       </c>
       <c r="G5">
-        <v>1950</v>
+        <v>2250</v>
       </c>
       <c r="H5" t="str">
-        <v>+1 REP</v>
+        <v>→ HOLD</v>
       </c>
       <c r="I5" t="str">
-        <v>RIR 1 &gt; target 0 → +1 rep</v>
+        <v>15@RIR1 on track</v>
       </c>
       <c r="J5" t="str">
         <v/>
@@ -9723,22 +9723,22 @@
         <v>4</v>
       </c>
       <c r="D6">
-        <v>22.5</v>
+        <v>25</v>
       </c>
       <c r="E6">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="F6">
         <v>0</v>
       </c>
       <c r="G6">
-        <v>1170</v>
+        <v>1000</v>
       </c>
       <c r="H6" t="str">
-        <v>→ HOLD</v>
+        <v>↑ WEIGHT</v>
       </c>
       <c r="I6" t="str">
-        <v>13@RIR0 on track</v>
+        <v>Hit 15@RIR0 = top of range → +2.5 kg</v>
       </c>
       <c r="J6" t="str">
         <v/>
@@ -9827,13 +9827,13 @@
         <v>32.5</v>
       </c>
       <c r="E2">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="F2">
         <v>3</v>
       </c>
       <c r="G2">
-        <v>780</v>
+        <v>975</v>
       </c>
       <c r="H2" t="str">
         <v>First session</v>
@@ -9865,13 +9865,13 @@
         <v>32.5</v>
       </c>
       <c r="E3">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="F3">
         <v>2</v>
       </c>
       <c r="G3">
-        <v>1170</v>
+        <v>1430</v>
       </c>
       <c r="H3" t="str">
         <v>+1 REP</v>
@@ -9903,13 +9903,13 @@
         <v>32.5</v>
       </c>
       <c r="E4">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="F4">
         <v>1</v>
       </c>
       <c r="G4">
-        <v>1625</v>
+        <v>1950</v>
       </c>
       <c r="H4" t="str">
         <v>+1 REP</v>
@@ -9941,19 +9941,19 @@
         <v>32.5</v>
       </c>
       <c r="E5">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="F5">
         <v>0</v>
       </c>
       <c r="G5">
-        <v>2145</v>
+        <v>2340</v>
       </c>
       <c r="H5" t="str">
-        <v>+1 REP</v>
+        <v>→ HOLD</v>
       </c>
       <c r="I5" t="str">
-        <v>RIR 1 &gt; target 0 → +1 rep</v>
+        <v>12@RIR1 on track</v>
       </c>
       <c r="J5" t="str">
         <v/>
@@ -9976,22 +9976,22 @@
         <v>5</v>
       </c>
       <c r="D6">
-        <v>30</v>
+        <v>32.5</v>
       </c>
       <c r="E6">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="F6">
         <v>0</v>
       </c>
       <c r="G6">
-        <v>1650</v>
+        <v>1300</v>
       </c>
       <c r="H6" t="str">
-        <v>→ HOLD</v>
+        <v>↑ WEIGHT</v>
       </c>
       <c r="I6" t="str">
-        <v>11@RIR0 on track</v>
+        <v>Hit 12@RIR0 = top of range → +2.5 kg</v>
       </c>
       <c r="J6" t="str">
         <v/>
@@ -10080,13 +10080,13 @@
         <v>30</v>
       </c>
       <c r="E2">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="F2">
         <v>3</v>
       </c>
       <c r="G2">
-        <v>720</v>
+        <v>900</v>
       </c>
       <c r="H2" t="str">
         <v>First session</v>
@@ -10118,13 +10118,13 @@
         <v>30</v>
       </c>
       <c r="E3">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="F3">
         <v>2</v>
       </c>
       <c r="G3">
-        <v>1080</v>
+        <v>1320</v>
       </c>
       <c r="H3" t="str">
         <v>+1 REP</v>
@@ -10156,13 +10156,13 @@
         <v>30</v>
       </c>
       <c r="E4">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="F4">
         <v>1</v>
       </c>
       <c r="G4">
-        <v>1500</v>
+        <v>1800</v>
       </c>
       <c r="H4" t="str">
         <v>+1 REP</v>
@@ -10194,19 +10194,19 @@
         <v>30</v>
       </c>
       <c r="E5">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="F5">
         <v>0</v>
       </c>
       <c r="G5">
-        <v>1980</v>
+        <v>2160</v>
       </c>
       <c r="H5" t="str">
-        <v>+1 REP</v>
+        <v>→ HOLD</v>
       </c>
       <c r="I5" t="str">
-        <v>RIR 1 &gt; target 0 → +1 rep</v>
+        <v>12@RIR1 on track</v>
       </c>
       <c r="J5" t="str">
         <v/>
@@ -10229,22 +10229,22 @@
         <v>4</v>
       </c>
       <c r="D6">
-        <v>27.5</v>
+        <v>30</v>
       </c>
       <c r="E6">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="F6">
         <v>0</v>
       </c>
       <c r="G6">
-        <v>1210</v>
+        <v>960</v>
       </c>
       <c r="H6" t="str">
-        <v>→ HOLD</v>
+        <v>↑ WEIGHT</v>
       </c>
       <c r="I6" t="str">
-        <v>11@RIR0 on track</v>
+        <v>Hit 12@RIR0 = top of range → +2.5 kg</v>
       </c>
       <c r="J6" t="str">
         <v/>
@@ -10333,13 +10333,13 @@
         <v>12.5</v>
       </c>
       <c r="E2">
-        <v>12</v>
+        <v>18</v>
       </c>
       <c r="F2">
         <v>3</v>
       </c>
       <c r="G2">
-        <v>300</v>
+        <v>450</v>
       </c>
       <c r="H2" t="str">
         <v>First session</v>
@@ -10371,13 +10371,13 @@
         <v>12.5</v>
       </c>
       <c r="E3">
-        <v>13</v>
+        <v>19</v>
       </c>
       <c r="F3">
         <v>2</v>
       </c>
       <c r="G3">
-        <v>487.5</v>
+        <v>712.5</v>
       </c>
       <c r="H3" t="str">
         <v>+1 REP</v>
@@ -10409,13 +10409,13 @@
         <v>12.5</v>
       </c>
       <c r="E4">
-        <v>14</v>
+        <v>20</v>
       </c>
       <c r="F4">
         <v>1</v>
       </c>
       <c r="G4">
-        <v>700</v>
+        <v>1000</v>
       </c>
       <c r="H4" t="str">
         <v>+1 REP</v>
@@ -10447,19 +10447,19 @@
         <v>12.5</v>
       </c>
       <c r="E5">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="F5">
         <v>0</v>
       </c>
       <c r="G5">
-        <v>937.5</v>
+        <v>1250</v>
       </c>
       <c r="H5" t="str">
-        <v>+1 REP</v>
+        <v>→ HOLD</v>
       </c>
       <c r="I5" t="str">
-        <v>RIR 1 &gt; target 0 → +1 rep</v>
+        <v>20@RIR1 on track</v>
       </c>
       <c r="J5" t="str">
         <v/>
@@ -10485,19 +10485,19 @@
         <v>12.5</v>
       </c>
       <c r="E6">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="F6">
         <v>0</v>
       </c>
       <c r="G6">
-        <v>562.5</v>
+        <v>450</v>
       </c>
       <c r="H6" t="str">
-        <v>→ HOLD</v>
+        <v>↑ WEIGHT</v>
       </c>
       <c r="I6" t="str">
-        <v>15@RIR0 on track</v>
+        <v>Hit 20@RIR0 = top of range → +2.5 kg</v>
       </c>
       <c r="J6" t="str">
         <v/>
@@ -10586,13 +10586,13 @@
         <v>80</v>
       </c>
       <c r="E2">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="F2">
         <v>3</v>
       </c>
       <c r="G2">
-        <v>1920</v>
+        <v>2400</v>
       </c>
       <c r="H2" t="str">
         <v>First session</v>
@@ -10624,13 +10624,13 @@
         <v>80</v>
       </c>
       <c r="E3">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="F3">
         <v>2</v>
       </c>
       <c r="G3">
-        <v>2880</v>
+        <v>3520</v>
       </c>
       <c r="H3" t="str">
         <v>+1 REP</v>
@@ -10662,13 +10662,13 @@
         <v>80</v>
       </c>
       <c r="E4">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="F4">
         <v>1</v>
       </c>
       <c r="G4">
-        <v>4000</v>
+        <v>4800</v>
       </c>
       <c r="H4" t="str">
         <v>+1 REP</v>
@@ -10700,19 +10700,19 @@
         <v>72.5</v>
       </c>
       <c r="E5">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="F5">
         <v>0</v>
       </c>
       <c r="G5">
-        <v>3190</v>
+        <v>3480</v>
       </c>
       <c r="H5" t="str">
-        <v>+1 REP</v>
+        <v>→ HOLD</v>
       </c>
       <c r="I5" t="str">
-        <v>RIR 1 &gt; target 0 → +1 rep</v>
+        <v>12@RIR1 on track</v>
       </c>
       <c r="J5" t="str">
         <v/>
@@ -10735,22 +10735,22 @@
         <v>4</v>
       </c>
       <c r="D6">
-        <v>65</v>
+        <v>67.5</v>
       </c>
       <c r="E6">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="F6">
         <v>0</v>
       </c>
       <c r="G6">
-        <v>2860</v>
+        <v>2160</v>
       </c>
       <c r="H6" t="str">
-        <v>→ HOLD</v>
+        <v>↑ WEIGHT</v>
       </c>
       <c r="I6" t="str">
-        <v>11@RIR0 on track</v>
+        <v>Hit 12@RIR0 = top of range → +2.5 kg</v>
       </c>
       <c r="J6" t="str">
         <v/>
@@ -10839,13 +10839,13 @@
         <v>40</v>
       </c>
       <c r="E2">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="F2">
         <v>3</v>
       </c>
       <c r="G2">
-        <v>1200</v>
+        <v>1560</v>
       </c>
       <c r="H2" t="str">
         <v>First session</v>
@@ -10877,13 +10877,13 @@
         <v>40</v>
       </c>
       <c r="E3">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="F3">
         <v>2</v>
       </c>
       <c r="G3">
-        <v>1760</v>
+        <v>2240</v>
       </c>
       <c r="H3" t="str">
         <v>+1 REP</v>
@@ -10915,13 +10915,13 @@
         <v>40</v>
       </c>
       <c r="E4">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="F4">
         <v>1</v>
       </c>
       <c r="G4">
-        <v>2400</v>
+        <v>3000</v>
       </c>
       <c r="H4" t="str">
         <v>+1 REP</v>
@@ -10953,19 +10953,19 @@
         <v>40</v>
       </c>
       <c r="E5">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="F5">
         <v>0</v>
       </c>
       <c r="G5">
-        <v>3120</v>
+        <v>3600</v>
       </c>
       <c r="H5" t="str">
-        <v>+1 REP</v>
+        <v>→ HOLD</v>
       </c>
       <c r="I5" t="str">
-        <v>RIR 1 &gt; target 0 → +1 rep</v>
+        <v>15@RIR1 on track</v>
       </c>
       <c r="J5" t="str">
         <v/>
@@ -10988,22 +10988,22 @@
         <v>4</v>
       </c>
       <c r="D6">
-        <v>35</v>
+        <v>37.5</v>
       </c>
       <c r="E6">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="F6">
         <v>0</v>
       </c>
       <c r="G6">
-        <v>1820</v>
+        <v>1500</v>
       </c>
       <c r="H6" t="str">
-        <v>→ HOLD</v>
+        <v>↑ WEIGHT</v>
       </c>
       <c r="I6" t="str">
-        <v>13@RIR0 on track</v>
+        <v>Hit 15@RIR0 = top of range → +2.5 kg</v>
       </c>
       <c r="J6" t="str">
         <v/>
@@ -11092,13 +11092,13 @@
         <v>80</v>
       </c>
       <c r="E2">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="F2">
         <v>3</v>
       </c>
       <c r="G2">
-        <v>1920</v>
+        <v>2400</v>
       </c>
       <c r="H2" t="str">
         <v>First session</v>
@@ -11130,13 +11130,13 @@
         <v>80</v>
       </c>
       <c r="E3">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="F3">
         <v>2</v>
       </c>
       <c r="G3">
-        <v>2880</v>
+        <v>3520</v>
       </c>
       <c r="H3" t="str">
         <v>+1 REP</v>
@@ -11168,13 +11168,13 @@
         <v>80</v>
       </c>
       <c r="E4">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="F4">
         <v>1</v>
       </c>
       <c r="G4">
-        <v>4000</v>
+        <v>4800</v>
       </c>
       <c r="H4" t="str">
         <v>+1 REP</v>
@@ -11206,19 +11206,19 @@
         <v>80</v>
       </c>
       <c r="E5">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="F5">
         <v>0</v>
       </c>
       <c r="G5">
-        <v>5280</v>
+        <v>5760</v>
       </c>
       <c r="H5" t="str">
-        <v>+1 REP</v>
+        <v>→ HOLD</v>
       </c>
       <c r="I5" t="str">
-        <v>RIR 1 &gt; target 0 → +1 rep</v>
+        <v>12@RIR1 on track</v>
       </c>
       <c r="J5" t="str">
         <v/>
@@ -11241,22 +11241,22 @@
         <v>6</v>
       </c>
       <c r="D6">
-        <v>80</v>
+        <v>82.5</v>
       </c>
       <c r="E6">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="F6">
         <v>0</v>
       </c>
       <c r="G6">
-        <v>5280</v>
+        <v>3960</v>
       </c>
       <c r="H6" t="str">
-        <v>→ HOLD</v>
+        <v>↑ WEIGHT</v>
       </c>
       <c r="I6" t="str">
-        <v>11@RIR0 on track</v>
+        <v>Hit 12@RIR0 = top of range → +2.5 kg</v>
       </c>
       <c r="J6" t="str">
         <v/>
@@ -11345,13 +11345,13 @@
         <v>30</v>
       </c>
       <c r="E2">
-        <v>10</v>
+        <v>18</v>
       </c>
       <c r="F2">
         <v>3</v>
       </c>
       <c r="G2">
-        <v>900</v>
+        <v>1620</v>
       </c>
       <c r="H2" t="str">
         <v>First session</v>
@@ -11383,13 +11383,13 @@
         <v>30</v>
       </c>
       <c r="E3">
-        <v>11</v>
+        <v>19</v>
       </c>
       <c r="F3">
         <v>2</v>
       </c>
       <c r="G3">
-        <v>1320</v>
+        <v>2280</v>
       </c>
       <c r="H3" t="str">
         <v>+1 REP</v>
@@ -11421,13 +11421,13 @@
         <v>30</v>
       </c>
       <c r="E4">
-        <v>12</v>
+        <v>20</v>
       </c>
       <c r="F4">
         <v>1</v>
       </c>
       <c r="G4">
-        <v>1800</v>
+        <v>3000</v>
       </c>
       <c r="H4" t="str">
         <v>+1 REP</v>
@@ -11459,19 +11459,19 @@
         <v>30</v>
       </c>
       <c r="E5">
-        <v>13</v>
+        <v>20</v>
       </c>
       <c r="F5">
         <v>0</v>
       </c>
       <c r="G5">
-        <v>2340</v>
+        <v>3600</v>
       </c>
       <c r="H5" t="str">
-        <v>+1 REP</v>
+        <v>→ HOLD</v>
       </c>
       <c r="I5" t="str">
-        <v>RIR 1 &gt; target 0 → +1 rep</v>
+        <v>20@RIR1 on track</v>
       </c>
       <c r="J5" t="str">
         <v/>
@@ -11494,22 +11494,22 @@
         <v>6</v>
       </c>
       <c r="D6">
-        <v>30</v>
+        <v>32.5</v>
       </c>
       <c r="E6">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="F6">
         <v>0</v>
       </c>
       <c r="G6">
-        <v>2340</v>
+        <v>1950</v>
       </c>
       <c r="H6" t="str">
-        <v>→ HOLD</v>
+        <v>↑ WEIGHT</v>
       </c>
       <c r="I6" t="str">
-        <v>13@RIR0 on track</v>
+        <v>Hit 20@RIR0 = top of range → +2.5 kg</v>
       </c>
       <c r="J6" t="str">
         <v/>
@@ -11614,19 +11614,19 @@
         <v>32.5</v>
       </c>
       <c r="E2">
-        <v>30</v>
+        <v>32.5</v>
       </c>
       <c r="F2">
-        <v>-2.5</v>
+        <v>0</v>
       </c>
       <c r="G2">
+        <v>10</v>
+      </c>
+      <c r="H2">
         <v>8</v>
       </c>
-      <c r="H2">
-        <v>11</v>
-      </c>
       <c r="I2">
-        <v>3</v>
+        <v>-2</v>
       </c>
       <c r="J2">
         <v>3</v>
@@ -11638,16 +11638,16 @@
         <v>2</v>
       </c>
       <c r="M2">
-        <v>780</v>
+        <v>975</v>
       </c>
       <c r="N2">
-        <v>1650</v>
+        <v>1300</v>
       </c>
       <c r="O2">
-        <v>870</v>
+        <v>325</v>
       </c>
       <c r="P2" t="str">
-        <v>111.5%</v>
+        <v>33.3%</v>
       </c>
     </row>
     <row r="3">
@@ -11664,19 +11664,19 @@
         <v>60</v>
       </c>
       <c r="E3">
-        <v>57.5</v>
+        <v>60</v>
       </c>
       <c r="F3">
-        <v>-2.5</v>
+        <v>0</v>
       </c>
       <c r="G3">
+        <v>13</v>
+      </c>
+      <c r="H3">
         <v>10</v>
       </c>
-      <c r="H3">
-        <v>13</v>
-      </c>
       <c r="I3">
-        <v>3</v>
+        <v>-3</v>
       </c>
       <c r="J3">
         <v>3</v>
@@ -11688,16 +11688,16 @@
         <v>2</v>
       </c>
       <c r="M3">
-        <v>1800</v>
+        <v>2340</v>
       </c>
       <c r="N3">
-        <v>3737.5</v>
+        <v>3000</v>
       </c>
       <c r="O3">
-        <v>1937.5</v>
+        <v>660</v>
       </c>
       <c r="P3" t="str">
-        <v>107.6%</v>
+        <v>28.2%</v>
       </c>
     </row>
     <row r="4">
@@ -11720,13 +11720,13 @@
         <v>0</v>
       </c>
       <c r="G4">
+        <v>18</v>
+      </c>
+      <c r="H4">
         <v>12</v>
       </c>
-      <c r="H4">
-        <v>15</v>
-      </c>
       <c r="I4">
-        <v>3</v>
+        <v>-6</v>
       </c>
       <c r="J4">
         <v>3</v>
@@ -11738,16 +11738,16 @@
         <v>3</v>
       </c>
       <c r="M4">
-        <v>360</v>
+        <v>540</v>
       </c>
       <c r="N4">
-        <v>900</v>
+        <v>720</v>
       </c>
       <c r="O4">
-        <v>540</v>
+        <v>180</v>
       </c>
       <c r="P4" t="str">
-        <v>150.0%</v>
+        <v>33.3%</v>
       </c>
     </row>
     <row r="5">
@@ -11764,19 +11764,19 @@
         <v>25</v>
       </c>
       <c r="E5">
-        <v>25</v>
+        <v>27.5</v>
       </c>
       <c r="F5">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="G5">
+        <v>13</v>
+      </c>
+      <c r="H5">
         <v>10</v>
       </c>
-      <c r="H5">
-        <v>13</v>
-      </c>
       <c r="I5">
-        <v>3</v>
+        <v>-3</v>
       </c>
       <c r="J5">
         <v>3</v>
@@ -11788,16 +11788,16 @@
         <v>3</v>
       </c>
       <c r="M5">
-        <v>750</v>
+        <v>975</v>
       </c>
       <c r="N5">
-        <v>1950</v>
+        <v>1650</v>
       </c>
       <c r="O5">
-        <v>1200</v>
+        <v>675</v>
       </c>
       <c r="P5" t="str">
-        <v>160.0%</v>
+        <v>69.2%</v>
       </c>
     </row>
     <row r="6">
@@ -11814,19 +11814,19 @@
         <v>55</v>
       </c>
       <c r="E6">
-        <v>50</v>
+        <v>52.5</v>
       </c>
       <c r="F6">
-        <v>-5</v>
+        <v>-2.5</v>
       </c>
       <c r="G6">
+        <v>10</v>
+      </c>
+      <c r="H6">
         <v>8</v>
       </c>
-      <c r="H6">
-        <v>11</v>
-      </c>
       <c r="I6">
-        <v>3</v>
+        <v>-2</v>
       </c>
       <c r="J6">
         <v>3</v>
@@ -11838,16 +11838,16 @@
         <v>1</v>
       </c>
       <c r="M6">
-        <v>1320</v>
+        <v>1650</v>
       </c>
       <c r="N6">
-        <v>2200</v>
+        <v>1680</v>
       </c>
       <c r="O6">
-        <v>880</v>
+        <v>30</v>
       </c>
       <c r="P6" t="str">
-        <v>66.7%</v>
+        <v>1.8%</v>
       </c>
     </row>
     <row r="7">
@@ -11864,19 +11864,19 @@
         <v>60</v>
       </c>
       <c r="E7">
-        <v>55</v>
+        <v>57.5</v>
       </c>
       <c r="F7">
-        <v>-5</v>
+        <v>-2.5</v>
       </c>
       <c r="G7">
+        <v>10</v>
+      </c>
+      <c r="H7">
         <v>8</v>
       </c>
-      <c r="H7">
-        <v>11</v>
-      </c>
       <c r="I7">
-        <v>3</v>
+        <v>-2</v>
       </c>
       <c r="J7">
         <v>3</v>
@@ -11888,16 +11888,16 @@
         <v>1</v>
       </c>
       <c r="M7">
-        <v>1440</v>
+        <v>1800</v>
       </c>
       <c r="N7">
-        <v>2420</v>
+        <v>1840</v>
       </c>
       <c r="O7">
-        <v>980</v>
+        <v>40</v>
       </c>
       <c r="P7" t="str">
-        <v>68.1%</v>
+        <v>2.2%</v>
       </c>
     </row>
     <row r="8">
@@ -11920,13 +11920,13 @@
         <v>0</v>
       </c>
       <c r="G8">
+        <v>13</v>
+      </c>
+      <c r="H8">
         <v>10</v>
       </c>
-      <c r="H8">
-        <v>13</v>
-      </c>
       <c r="I8">
-        <v>3</v>
+        <v>-3</v>
       </c>
       <c r="J8">
         <v>3</v>
@@ -11938,16 +11938,16 @@
         <v>1</v>
       </c>
       <c r="M8">
-        <v>375</v>
+        <v>487.5</v>
       </c>
       <c r="N8">
-        <v>650</v>
+        <v>500</v>
       </c>
       <c r="O8">
-        <v>275</v>
+        <v>12.5</v>
       </c>
       <c r="P8" t="str">
-        <v>73.3%</v>
+        <v>2.6%</v>
       </c>
     </row>
     <row r="9">
@@ -11964,19 +11964,19 @@
         <v>15</v>
       </c>
       <c r="E9">
-        <v>12.5</v>
+        <v>15</v>
       </c>
       <c r="F9">
-        <v>-2.5</v>
+        <v>0</v>
       </c>
       <c r="G9">
+        <v>13</v>
+      </c>
+      <c r="H9">
         <v>10</v>
       </c>
-      <c r="H9">
-        <v>13</v>
-      </c>
       <c r="I9">
-        <v>3</v>
+        <v>-3</v>
       </c>
       <c r="J9">
         <v>2</v>
@@ -11988,16 +11988,16 @@
         <v>1</v>
       </c>
       <c r="M9">
-        <v>300</v>
+        <v>390</v>
       </c>
       <c r="N9">
-        <v>487.5</v>
+        <v>450</v>
       </c>
       <c r="O9">
-        <v>187.5</v>
+        <v>60</v>
       </c>
       <c r="P9" t="str">
-        <v>62.5%</v>
+        <v>15.4%</v>
       </c>
     </row>
     <row r="10">
@@ -12014,19 +12014,19 @@
         <v>120</v>
       </c>
       <c r="E10">
-        <v>97.5</v>
+        <v>100</v>
       </c>
       <c r="F10">
-        <v>-22.5</v>
+        <v>-20</v>
       </c>
       <c r="G10">
+        <v>10</v>
+      </c>
+      <c r="H10">
         <v>8</v>
       </c>
-      <c r="H10">
-        <v>11</v>
-      </c>
       <c r="I10">
-        <v>3</v>
+        <v>-2</v>
       </c>
       <c r="J10">
         <v>3</v>
@@ -12038,16 +12038,16 @@
         <v>1</v>
       </c>
       <c r="M10">
-        <v>2880</v>
+        <v>3600</v>
       </c>
       <c r="N10">
-        <v>4290</v>
+        <v>3200</v>
       </c>
       <c r="O10">
-        <v>1410</v>
+        <v>-400</v>
       </c>
       <c r="P10" t="str">
-        <v>49.0%</v>
+        <v>-11.1%</v>
       </c>
     </row>
     <row r="11">
@@ -12064,19 +12064,19 @@
         <v>50</v>
       </c>
       <c r="E11">
-        <v>40</v>
+        <v>42.5</v>
       </c>
       <c r="F11">
-        <v>-10</v>
+        <v>-7.5</v>
       </c>
       <c r="G11">
+        <v>18</v>
+      </c>
+      <c r="H11">
         <v>12</v>
       </c>
-      <c r="H11">
-        <v>15</v>
-      </c>
       <c r="I11">
-        <v>3</v>
+        <v>-6</v>
       </c>
       <c r="J11">
         <v>3</v>
@@ -12088,16 +12088,16 @@
         <v>1</v>
       </c>
       <c r="M11">
-        <v>1800</v>
+        <v>2700</v>
       </c>
       <c r="N11">
-        <v>2400</v>
+        <v>2040</v>
       </c>
       <c r="O11">
-        <v>600</v>
+        <v>-660</v>
       </c>
       <c r="P11" t="str">
-        <v>33.3%</v>
+        <v>-24.4%</v>
       </c>
     </row>
     <row r="12">
@@ -12114,19 +12114,19 @@
         <v>60</v>
       </c>
       <c r="E12">
-        <v>55</v>
+        <v>57.5</v>
       </c>
       <c r="F12">
-        <v>-5</v>
+        <v>-2.5</v>
       </c>
       <c r="G12">
+        <v>10</v>
+      </c>
+      <c r="H12">
         <v>8</v>
       </c>
-      <c r="H12">
-        <v>11</v>
-      </c>
       <c r="I12">
-        <v>3</v>
+        <v>-2</v>
       </c>
       <c r="J12">
         <v>3</v>
@@ -12138,16 +12138,16 @@
         <v>1</v>
       </c>
       <c r="M12">
-        <v>1440</v>
+        <v>1800</v>
       </c>
       <c r="N12">
-        <v>2420</v>
+        <v>1840</v>
       </c>
       <c r="O12">
-        <v>980</v>
+        <v>40</v>
       </c>
       <c r="P12" t="str">
-        <v>68.1%</v>
+        <v>2.2%</v>
       </c>
     </row>
     <row r="13">
@@ -12164,19 +12164,19 @@
         <v>40</v>
       </c>
       <c r="E13">
-        <v>40</v>
+        <v>42.5</v>
       </c>
       <c r="F13">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="G13">
+        <v>18</v>
+      </c>
+      <c r="H13">
         <v>10</v>
       </c>
-      <c r="H13">
-        <v>13</v>
-      </c>
       <c r="I13">
-        <v>3</v>
+        <v>-8</v>
       </c>
       <c r="J13">
         <v>4</v>
@@ -12188,16 +12188,16 @@
         <v>3</v>
       </c>
       <c r="M13">
-        <v>1600</v>
+        <v>2880</v>
       </c>
       <c r="N13">
-        <v>3640</v>
+        <v>2975</v>
       </c>
       <c r="O13">
-        <v>2040</v>
+        <v>95</v>
       </c>
       <c r="P13" t="str">
-        <v>127.5%</v>
+        <v>3.3%</v>
       </c>
     </row>
     <row r="14">
@@ -12214,19 +12214,19 @@
         <v>35</v>
       </c>
       <c r="E14">
-        <v>32.5</v>
+        <v>35</v>
       </c>
       <c r="F14">
-        <v>-2.5</v>
+        <v>0</v>
       </c>
       <c r="G14">
+        <v>10</v>
+      </c>
+      <c r="H14">
         <v>8</v>
       </c>
-      <c r="H14">
-        <v>11</v>
-      </c>
       <c r="I14">
-        <v>3</v>
+        <v>-2</v>
       </c>
       <c r="J14">
         <v>3</v>
@@ -12238,16 +12238,16 @@
         <v>2</v>
       </c>
       <c r="M14">
-        <v>840</v>
+        <v>1050</v>
       </c>
       <c r="N14">
-        <v>1787.5</v>
+        <v>1400</v>
       </c>
       <c r="O14">
-        <v>947.5</v>
+        <v>350</v>
       </c>
       <c r="P14" t="str">
-        <v>112.8%</v>
+        <v>33.3%</v>
       </c>
     </row>
     <row r="15">
@@ -12264,19 +12264,19 @@
         <v>45</v>
       </c>
       <c r="E15">
-        <v>42.5</v>
+        <v>45</v>
       </c>
       <c r="F15">
-        <v>-2.5</v>
+        <v>0</v>
       </c>
       <c r="G15">
+        <v>18</v>
+      </c>
+      <c r="H15">
         <v>12</v>
       </c>
-      <c r="H15">
-        <v>15</v>
-      </c>
       <c r="I15">
-        <v>3</v>
+        <v>-6</v>
       </c>
       <c r="J15">
         <v>3</v>
@@ -12288,16 +12288,16 @@
         <v>2</v>
       </c>
       <c r="M15">
-        <v>1620</v>
+        <v>2430</v>
       </c>
       <c r="N15">
-        <v>3187.5</v>
+        <v>2700</v>
       </c>
       <c r="O15">
-        <v>1567.5</v>
+        <v>270</v>
       </c>
       <c r="P15" t="str">
-        <v>96.8%</v>
+        <v>11.1%</v>
       </c>
     </row>
     <row r="16">
@@ -12314,19 +12314,19 @@
         <v>40</v>
       </c>
       <c r="E16">
-        <v>40</v>
+        <v>42.5</v>
       </c>
       <c r="F16">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="G16">
+        <v>13</v>
+      </c>
+      <c r="H16">
         <v>10</v>
       </c>
-      <c r="H16">
-        <v>13</v>
-      </c>
       <c r="I16">
-        <v>3</v>
+        <v>-3</v>
       </c>
       <c r="J16">
         <v>3</v>
@@ -12338,16 +12338,16 @@
         <v>3</v>
       </c>
       <c r="M16">
-        <v>1200</v>
+        <v>1560</v>
       </c>
       <c r="N16">
-        <v>3120</v>
+        <v>2550</v>
       </c>
       <c r="O16">
-        <v>1920</v>
+        <v>990</v>
       </c>
       <c r="P16" t="str">
-        <v>160.0%</v>
+        <v>63.5%</v>
       </c>
     </row>
     <row r="17">
@@ -12364,19 +12364,19 @@
         <v>20</v>
       </c>
       <c r="E17">
-        <v>20</v>
+        <v>22.5</v>
       </c>
       <c r="F17">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="G17">
+        <v>18</v>
+      </c>
+      <c r="H17">
         <v>12</v>
       </c>
-      <c r="H17">
-        <v>15</v>
-      </c>
       <c r="I17">
-        <v>3</v>
+        <v>-6</v>
       </c>
       <c r="J17">
         <v>3</v>
@@ -12388,16 +12388,16 @@
         <v>3</v>
       </c>
       <c r="M17">
-        <v>720</v>
+        <v>1080</v>
       </c>
       <c r="N17">
-        <v>1800</v>
+        <v>1620</v>
       </c>
       <c r="O17">
-        <v>1080</v>
+        <v>540</v>
       </c>
       <c r="P17" t="str">
-        <v>150.0%</v>
+        <v>50.0%</v>
       </c>
     </row>
     <row r="18">
@@ -12414,19 +12414,19 @@
         <v>50</v>
       </c>
       <c r="E18">
-        <v>45</v>
+        <v>47.5</v>
       </c>
       <c r="F18">
-        <v>-5</v>
+        <v>-2.5</v>
       </c>
       <c r="G18">
+        <v>10</v>
+      </c>
+      <c r="H18">
         <v>8</v>
       </c>
-      <c r="H18">
-        <v>11</v>
-      </c>
       <c r="I18">
-        <v>3</v>
+        <v>-2</v>
       </c>
       <c r="J18">
         <v>3</v>
@@ -12438,16 +12438,16 @@
         <v>1</v>
       </c>
       <c r="M18">
-        <v>1200</v>
+        <v>1500</v>
       </c>
       <c r="N18">
-        <v>1980</v>
+        <v>1520</v>
       </c>
       <c r="O18">
-        <v>780</v>
+        <v>20</v>
       </c>
       <c r="P18" t="str">
-        <v>65.0%</v>
+        <v>1.3%</v>
       </c>
     </row>
     <row r="19">
@@ -12464,19 +12464,19 @@
         <v>25</v>
       </c>
       <c r="E19">
-        <v>22.5</v>
+        <v>25</v>
       </c>
       <c r="F19">
-        <v>-2.5</v>
+        <v>0</v>
       </c>
       <c r="G19">
+        <v>13</v>
+      </c>
+      <c r="H19">
         <v>10</v>
       </c>
-      <c r="H19">
-        <v>13</v>
-      </c>
       <c r="I19">
-        <v>3</v>
+        <v>-3</v>
       </c>
       <c r="J19">
         <v>3</v>
@@ -12488,16 +12488,16 @@
         <v>1</v>
       </c>
       <c r="M19">
-        <v>750</v>
+        <v>975</v>
       </c>
       <c r="N19">
-        <v>1170</v>
+        <v>1000</v>
       </c>
       <c r="O19">
-        <v>420</v>
+        <v>25</v>
       </c>
       <c r="P19" t="str">
-        <v>56.0%</v>
+        <v>2.6%</v>
       </c>
     </row>
     <row r="20">
@@ -12514,19 +12514,19 @@
         <v>30</v>
       </c>
       <c r="E20">
-        <v>27.5</v>
+        <v>30</v>
       </c>
       <c r="F20">
-        <v>-2.5</v>
+        <v>0</v>
       </c>
       <c r="G20">
+        <v>10</v>
+      </c>
+      <c r="H20">
         <v>8</v>
       </c>
-      <c r="H20">
-        <v>11</v>
-      </c>
       <c r="I20">
-        <v>3</v>
+        <v>-2</v>
       </c>
       <c r="J20">
         <v>3</v>
@@ -12538,16 +12538,16 @@
         <v>1</v>
       </c>
       <c r="M20">
-        <v>720</v>
+        <v>900</v>
       </c>
       <c r="N20">
-        <v>1210</v>
+        <v>960</v>
       </c>
       <c r="O20">
-        <v>490</v>
+        <v>60</v>
       </c>
       <c r="P20" t="str">
-        <v>68.1%</v>
+        <v>6.7%</v>
       </c>
     </row>
     <row r="21">
@@ -12570,13 +12570,13 @@
         <v>0</v>
       </c>
       <c r="G21">
+        <v>18</v>
+      </c>
+      <c r="H21">
         <v>12</v>
       </c>
-      <c r="H21">
-        <v>15</v>
-      </c>
       <c r="I21">
-        <v>3</v>
+        <v>-6</v>
       </c>
       <c r="J21">
         <v>2</v>
@@ -12588,16 +12588,16 @@
         <v>1</v>
       </c>
       <c r="M21">
-        <v>300</v>
+        <v>450</v>
       </c>
       <c r="N21">
-        <v>562.5</v>
+        <v>450</v>
       </c>
       <c r="O21">
-        <v>262.5</v>
+        <v>0</v>
       </c>
       <c r="P21" t="str">
-        <v>87.5%</v>
+        <v>0.0%</v>
       </c>
     </row>
     <row r="22">
@@ -12614,19 +12614,19 @@
         <v>80</v>
       </c>
       <c r="E22">
-        <v>65</v>
+        <v>67.5</v>
       </c>
       <c r="F22">
-        <v>-15</v>
+        <v>-12.5</v>
       </c>
       <c r="G22">
+        <v>10</v>
+      </c>
+      <c r="H22">
         <v>8</v>
       </c>
-      <c r="H22">
-        <v>11</v>
-      </c>
       <c r="I22">
-        <v>3</v>
+        <v>-2</v>
       </c>
       <c r="J22">
         <v>3</v>
@@ -12638,16 +12638,16 @@
         <v>1</v>
       </c>
       <c r="M22">
-        <v>1920</v>
+        <v>2400</v>
       </c>
       <c r="N22">
-        <v>2860</v>
+        <v>2160</v>
       </c>
       <c r="O22">
-        <v>940</v>
+        <v>-240</v>
       </c>
       <c r="P22" t="str">
-        <v>49.0%</v>
+        <v>-10.0%</v>
       </c>
     </row>
     <row r="23">
@@ -12664,19 +12664,19 @@
         <v>40</v>
       </c>
       <c r="E23">
-        <v>35</v>
+        <v>37.5</v>
       </c>
       <c r="F23">
-        <v>-5</v>
+        <v>-2.5</v>
       </c>
       <c r="G23">
+        <v>13</v>
+      </c>
+      <c r="H23">
         <v>10</v>
       </c>
-      <c r="H23">
-        <v>13</v>
-      </c>
       <c r="I23">
-        <v>3</v>
+        <v>-3</v>
       </c>
       <c r="J23">
         <v>3</v>
@@ -12688,16 +12688,16 @@
         <v>1</v>
       </c>
       <c r="M23">
-        <v>1200</v>
+        <v>1560</v>
       </c>
       <c r="N23">
-        <v>1820</v>
+        <v>1500</v>
       </c>
       <c r="O23">
-        <v>620</v>
+        <v>-60</v>
       </c>
       <c r="P23" t="str">
-        <v>51.7%</v>
+        <v>-3.8%</v>
       </c>
     </row>
     <row r="24">
@@ -12714,19 +12714,19 @@
         <v>80</v>
       </c>
       <c r="E24">
-        <v>80</v>
+        <v>82.5</v>
       </c>
       <c r="F24">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="G24">
+        <v>10</v>
+      </c>
+      <c r="H24">
         <v>8</v>
       </c>
-      <c r="H24">
-        <v>11</v>
-      </c>
       <c r="I24">
-        <v>3</v>
+        <v>-2</v>
       </c>
       <c r="J24">
         <v>3</v>
@@ -12738,16 +12738,16 @@
         <v>3</v>
       </c>
       <c r="M24">
-        <v>1920</v>
+        <v>2400</v>
       </c>
       <c r="N24">
-        <v>5280</v>
+        <v>3960</v>
       </c>
       <c r="O24">
-        <v>3360</v>
+        <v>1560</v>
       </c>
       <c r="P24" t="str">
-        <v>175.0%</v>
+        <v>65.0%</v>
       </c>
     </row>
     <row r="25">
@@ -12764,19 +12764,19 @@
         <v>30</v>
       </c>
       <c r="E25">
-        <v>30</v>
+        <v>32.5</v>
       </c>
       <c r="F25">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="G25">
+        <v>18</v>
+      </c>
+      <c r="H25">
         <v>10</v>
       </c>
-      <c r="H25">
-        <v>13</v>
-      </c>
       <c r="I25">
-        <v>3</v>
+        <v>-8</v>
       </c>
       <c r="J25">
         <v>3</v>
@@ -12788,16 +12788,16 @@
         <v>3</v>
       </c>
       <c r="M25">
-        <v>900</v>
+        <v>1620</v>
       </c>
       <c r="N25">
-        <v>2340</v>
+        <v>1950</v>
       </c>
       <c r="O25">
-        <v>1440</v>
+        <v>330</v>
       </c>
       <c r="P25" t="str">
-        <v>160.0%</v>
+        <v>20.4%</v>
       </c>
     </row>
   </sheetData>
@@ -12877,13 +12877,13 @@
         <v>60</v>
       </c>
       <c r="E2">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="F2">
         <v>3</v>
       </c>
       <c r="G2">
-        <v>1800</v>
+        <v>2340</v>
       </c>
       <c r="H2" t="str">
         <v>First session</v>
@@ -12915,13 +12915,13 @@
         <v>60</v>
       </c>
       <c r="E3">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="F3">
         <v>2</v>
       </c>
       <c r="G3">
-        <v>2640</v>
+        <v>3360</v>
       </c>
       <c r="H3" t="str">
         <v>+1 REP</v>
@@ -12953,13 +12953,13 @@
         <v>60</v>
       </c>
       <c r="E4">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="F4">
         <v>1</v>
       </c>
       <c r="G4">
-        <v>3600</v>
+        <v>4500</v>
       </c>
       <c r="H4" t="str">
         <v>+1 REP</v>
@@ -12991,19 +12991,19 @@
         <v>60</v>
       </c>
       <c r="E5">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="F5">
         <v>0</v>
       </c>
       <c r="G5">
-        <v>4680</v>
+        <v>5400</v>
       </c>
       <c r="H5" t="str">
-        <v>+1 REP</v>
+        <v>→ HOLD</v>
       </c>
       <c r="I5" t="str">
-        <v>RIR 1 &gt; target 0 → +1 rep</v>
+        <v>15@RIR1 on track</v>
       </c>
       <c r="J5" t="str">
         <v/>
@@ -13026,22 +13026,22 @@
         <v>5</v>
       </c>
       <c r="D6">
-        <v>57.5</v>
+        <v>60</v>
       </c>
       <c r="E6">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="F6">
         <v>0</v>
       </c>
       <c r="G6">
-        <v>3737.5</v>
+        <v>3000</v>
       </c>
       <c r="H6" t="str">
-        <v>→ HOLD</v>
+        <v>↑ WEIGHT</v>
       </c>
       <c r="I6" t="str">
-        <v>13@RIR0 on track</v>
+        <v>Hit 15@RIR0 = top of range → +2.5 kg</v>
       </c>
       <c r="J6" t="str">
         <v/>
@@ -13130,13 +13130,13 @@
         <v>10</v>
       </c>
       <c r="E2">
-        <v>12</v>
+        <v>18</v>
       </c>
       <c r="F2">
         <v>3</v>
       </c>
       <c r="G2">
-        <v>360</v>
+        <v>540</v>
       </c>
       <c r="H2" t="str">
         <v>First session</v>
@@ -13168,13 +13168,13 @@
         <v>10</v>
       </c>
       <c r="E3">
-        <v>13</v>
+        <v>19</v>
       </c>
       <c r="F3">
         <v>2</v>
       </c>
       <c r="G3">
-        <v>520</v>
+        <v>760</v>
       </c>
       <c r="H3" t="str">
         <v>+1 REP</v>
@@ -13206,13 +13206,13 @@
         <v>10</v>
       </c>
       <c r="E4">
-        <v>14</v>
+        <v>20</v>
       </c>
       <c r="F4">
         <v>1</v>
       </c>
       <c r="G4">
-        <v>700</v>
+        <v>1000</v>
       </c>
       <c r="H4" t="str">
         <v>+1 REP</v>
@@ -13244,19 +13244,19 @@
         <v>10</v>
       </c>
       <c r="E5">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="F5">
         <v>0</v>
       </c>
       <c r="G5">
-        <v>900</v>
+        <v>1200</v>
       </c>
       <c r="H5" t="str">
-        <v>+1 REP</v>
+        <v>→ HOLD</v>
       </c>
       <c r="I5" t="str">
-        <v>RIR 1 &gt; target 0 → +1 rep</v>
+        <v>20@RIR1 on track</v>
       </c>
       <c r="J5" t="str">
         <v/>
@@ -13282,19 +13282,19 @@
         <v>10</v>
       </c>
       <c r="E6">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="F6">
         <v>0</v>
       </c>
       <c r="G6">
-        <v>900</v>
+        <v>720</v>
       </c>
       <c r="H6" t="str">
-        <v>→ HOLD</v>
+        <v>↑ WEIGHT</v>
       </c>
       <c r="I6" t="str">
-        <v>15@RIR0 on track</v>
+        <v>Hit 20@RIR0 = top of range → +2.5 kg</v>
       </c>
       <c r="J6" t="str">
         <v/>
@@ -13383,13 +13383,13 @@
         <v>25</v>
       </c>
       <c r="E2">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="F2">
         <v>3</v>
       </c>
       <c r="G2">
-        <v>750</v>
+        <v>975</v>
       </c>
       <c r="H2" t="str">
         <v>First session</v>
@@ -13421,13 +13421,13 @@
         <v>25</v>
       </c>
       <c r="E3">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="F3">
         <v>2</v>
       </c>
       <c r="G3">
-        <v>1100</v>
+        <v>1400</v>
       </c>
       <c r="H3" t="str">
         <v>+1 REP</v>
@@ -13459,13 +13459,13 @@
         <v>25</v>
       </c>
       <c r="E4">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="F4">
         <v>1</v>
       </c>
       <c r="G4">
-        <v>1500</v>
+        <v>1875</v>
       </c>
       <c r="H4" t="str">
         <v>+1 REP</v>
@@ -13497,19 +13497,19 @@
         <v>25</v>
       </c>
       <c r="E5">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="F5">
         <v>0</v>
       </c>
       <c r="G5">
-        <v>1950</v>
+        <v>2250</v>
       </c>
       <c r="H5" t="str">
-        <v>+1 REP</v>
+        <v>→ HOLD</v>
       </c>
       <c r="I5" t="str">
-        <v>RIR 1 &gt; target 0 → +1 rep</v>
+        <v>15@RIR1 on track</v>
       </c>
       <c r="J5" t="str">
         <v/>
@@ -13532,22 +13532,22 @@
         <v>6</v>
       </c>
       <c r="D6">
-        <v>25</v>
+        <v>27.5</v>
       </c>
       <c r="E6">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="F6">
         <v>0</v>
       </c>
       <c r="G6">
-        <v>1950</v>
+        <v>1650</v>
       </c>
       <c r="H6" t="str">
-        <v>→ HOLD</v>
+        <v>↑ WEIGHT</v>
       </c>
       <c r="I6" t="str">
-        <v>13@RIR0 on track</v>
+        <v>Hit 15@RIR0 = top of range → +2.5 kg</v>
       </c>
       <c r="J6" t="str">
         <v/>
@@ -13636,13 +13636,13 @@
         <v>55</v>
       </c>
       <c r="E2">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="F2">
         <v>3</v>
       </c>
       <c r="G2">
-        <v>1320</v>
+        <v>1650</v>
       </c>
       <c r="H2" t="str">
         <v>First session</v>
@@ -13674,13 +13674,13 @@
         <v>55</v>
       </c>
       <c r="E3">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="F3">
         <v>2</v>
       </c>
       <c r="G3">
-        <v>1980</v>
+        <v>2420</v>
       </c>
       <c r="H3" t="str">
         <v>+1 REP</v>
@@ -13712,13 +13712,13 @@
         <v>55</v>
       </c>
       <c r="E4">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="F4">
         <v>1</v>
       </c>
       <c r="G4">
-        <v>2750</v>
+        <v>3300</v>
       </c>
       <c r="H4" t="str">
         <v>+1 REP</v>
@@ -13750,19 +13750,19 @@
         <v>55</v>
       </c>
       <c r="E5">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="F5">
         <v>0</v>
       </c>
       <c r="G5">
-        <v>3630</v>
+        <v>3960</v>
       </c>
       <c r="H5" t="str">
-        <v>+1 REP</v>
+        <v>→ HOLD</v>
       </c>
       <c r="I5" t="str">
-        <v>RIR 1 &gt; target 0 → +1 rep</v>
+        <v>12@RIR1 on track</v>
       </c>
       <c r="J5" t="str">
         <v/>
@@ -13785,22 +13785,22 @@
         <v>4</v>
       </c>
       <c r="D6">
-        <v>50</v>
+        <v>52.5</v>
       </c>
       <c r="E6">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="F6">
         <v>0</v>
       </c>
       <c r="G6">
-        <v>2200</v>
+        <v>1680</v>
       </c>
       <c r="H6" t="str">
-        <v>→ HOLD</v>
+        <v>↑ WEIGHT</v>
       </c>
       <c r="I6" t="str">
-        <v>11@RIR0 on track</v>
+        <v>Hit 12@RIR0 = top of range → +2.5 kg</v>
       </c>
       <c r="J6" t="str">
         <v/>
@@ -13889,13 +13889,13 @@
         <v>60</v>
       </c>
       <c r="E2">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="F2">
         <v>3</v>
       </c>
       <c r="G2">
-        <v>1440</v>
+        <v>1800</v>
       </c>
       <c r="H2" t="str">
         <v>First session</v>
@@ -13927,13 +13927,13 @@
         <v>60</v>
       </c>
       <c r="E3">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="F3">
         <v>2</v>
       </c>
       <c r="G3">
-        <v>2160</v>
+        <v>2640</v>
       </c>
       <c r="H3" t="str">
         <v>+1 REP</v>
@@ -13965,13 +13965,13 @@
         <v>60</v>
       </c>
       <c r="E4">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="F4">
         <v>1</v>
       </c>
       <c r="G4">
-        <v>3000</v>
+        <v>3600</v>
       </c>
       <c r="H4" t="str">
         <v>+1 REP</v>
@@ -14003,19 +14003,19 @@
         <v>60</v>
       </c>
       <c r="E5">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="F5">
         <v>0</v>
       </c>
       <c r="G5">
-        <v>3960</v>
+        <v>4320</v>
       </c>
       <c r="H5" t="str">
-        <v>+1 REP</v>
+        <v>→ HOLD</v>
       </c>
       <c r="I5" t="str">
-        <v>RIR 1 &gt; target 0 → +1 rep</v>
+        <v>12@RIR1 on track</v>
       </c>
       <c r="J5" t="str">
         <v/>
@@ -14038,22 +14038,22 @@
         <v>4</v>
       </c>
       <c r="D6">
-        <v>55</v>
+        <v>57.5</v>
       </c>
       <c r="E6">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="F6">
         <v>0</v>
       </c>
       <c r="G6">
-        <v>2420</v>
+        <v>1840</v>
       </c>
       <c r="H6" t="str">
-        <v>→ HOLD</v>
+        <v>↑ WEIGHT</v>
       </c>
       <c r="I6" t="str">
-        <v>11@RIR0 on track</v>
+        <v>Hit 12@RIR0 = top of range → +2.5 kg</v>
       </c>
       <c r="J6" t="str">
         <v/>
@@ -14142,13 +14142,13 @@
         <v>12.5</v>
       </c>
       <c r="E2">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="F2">
         <v>3</v>
       </c>
       <c r="G2">
-        <v>375</v>
+        <v>487.5</v>
       </c>
       <c r="H2" t="str">
         <v>First session</v>
@@ -14180,13 +14180,13 @@
         <v>12.5</v>
       </c>
       <c r="E3">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="F3">
         <v>2</v>
       </c>
       <c r="G3">
-        <v>550</v>
+        <v>700</v>
       </c>
       <c r="H3" t="str">
         <v>+1 REP</v>
@@ -14218,13 +14218,13 @@
         <v>12.5</v>
       </c>
       <c r="E4">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="F4">
         <v>1</v>
       </c>
       <c r="G4">
-        <v>750</v>
+        <v>937.5</v>
       </c>
       <c r="H4" t="str">
         <v>+1 REP</v>
@@ -14256,19 +14256,19 @@
         <v>12.5</v>
       </c>
       <c r="E5">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="F5">
         <v>0</v>
       </c>
       <c r="G5">
-        <v>975</v>
+        <v>1125</v>
       </c>
       <c r="H5" t="str">
-        <v>+1 REP</v>
+        <v>→ HOLD</v>
       </c>
       <c r="I5" t="str">
-        <v>RIR 1 &gt; target 0 → +1 rep</v>
+        <v>15@RIR1 on track</v>
       </c>
       <c r="J5" t="str">
         <v/>
@@ -14294,19 +14294,19 @@
         <v>12.5</v>
       </c>
       <c r="E6">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="F6">
         <v>0</v>
       </c>
       <c r="G6">
-        <v>650</v>
+        <v>500</v>
       </c>
       <c r="H6" t="str">
-        <v>→ HOLD</v>
+        <v>↑ WEIGHT</v>
       </c>
       <c r="I6" t="str">
-        <v>13@RIR0 on track</v>
+        <v>Hit 15@RIR0 = top of range → +2.5 kg</v>
       </c>
       <c r="J6" t="str">
         <v/>
@@ -14395,13 +14395,13 @@
         <v>15</v>
       </c>
       <c r="E2">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="F2">
         <v>3</v>
       </c>
       <c r="G2">
-        <v>300</v>
+        <v>390</v>
       </c>
       <c r="H2" t="str">
         <v>First session</v>
@@ -14433,13 +14433,13 @@
         <v>15</v>
       </c>
       <c r="E3">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="F3">
         <v>2</v>
       </c>
       <c r="G3">
-        <v>495</v>
+        <v>630</v>
       </c>
       <c r="H3" t="str">
         <v>+1 REP</v>
@@ -14471,13 +14471,13 @@
         <v>15</v>
       </c>
       <c r="E4">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="F4">
         <v>1</v>
       </c>
       <c r="G4">
-        <v>720</v>
+        <v>900</v>
       </c>
       <c r="H4" t="str">
         <v>+1 REP</v>
@@ -14509,19 +14509,19 @@
         <v>15</v>
       </c>
       <c r="E5">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="F5">
         <v>0</v>
       </c>
       <c r="G5">
-        <v>975</v>
+        <v>1125</v>
       </c>
       <c r="H5" t="str">
-        <v>+1 REP</v>
+        <v>→ HOLD</v>
       </c>
       <c r="I5" t="str">
-        <v>RIR 1 &gt; target 0 → +1 rep</v>
+        <v>15@RIR1 on track</v>
       </c>
       <c r="J5" t="str">
         <v/>
@@ -14544,22 +14544,22 @@
         <v>3</v>
       </c>
       <c r="D6">
-        <v>12.5</v>
+        <v>15</v>
       </c>
       <c r="E6">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="F6">
         <v>0</v>
       </c>
       <c r="G6">
-        <v>487.5</v>
+        <v>450</v>
       </c>
       <c r="H6" t="str">
-        <v>→ HOLD</v>
+        <v>↑ WEIGHT</v>
       </c>
       <c r="I6" t="str">
-        <v>13@RIR0 on track</v>
+        <v>Hit 15@RIR0 = top of range → +2.5 kg</v>
       </c>
       <c r="J6" t="str">
         <v/>
